--- a/docs/runbooks/コマ表アプリ動作チェックリスト（全項目・網羅版）.xlsx
+++ b/docs/runbooks/コマ表アプリ動作チェックリスト（全項目・網羅版）.xlsx
@@ -13,7 +13,7 @@
     <sheet name="確認情報" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'全項目チェック'!$A$3:$I$310</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'全項目チェック'!$A$3:$I$313</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'全項目チェック'!$3:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -789,7 +789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I310"/>
+  <dimension ref="A1:I313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2947,17 +2947,17 @@
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>開発者</t>
+          <t>室長</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>（開発用教室のみ）「他教室のバックアップを開発用教室に読み込む」を使う</t>
+          <t>（開発用教室・テスト教室のみ）「他教室のバックアップをこの教室に読み込む」で読み込み元を取得する</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>開発用教室にだけ入る。日程表のQRは自教室が発行し直したものになり、コピー元(本番)のQRは出ない</t>
+          <t>教室とバックアップ時点の一覧が取得できる（本番3教室が読み込み元として選べる）</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
@@ -2977,34 +2977,34 @@
       <c r="A61" s="6" t="n">
         <v>58</v>
       </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>7.コマ表の表示</t>
+      <c r="B61" s="8" t="inlineStr">
+        <is>
+          <t>6.復元・初期設定</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>共通</t>
+          <t>室長</t>
         </is>
       </c>
       <c r="D61" s="8" t="inlineStr">
         <is>
-          <t>コマ表を開く</t>
+          <t>本番教室を選んで「この教室へ読み込む」を実行する</t>
         </is>
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>曜日×時限の表が表示される</t>
+          <t>確認のあと、いま開いている検証用教室にだけ読み込まれる。読み込み元の教室は変わらない（読み込み後は「保存」が必要）</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="G61" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G61" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H61" s="6" t="n"/>
@@ -3016,22 +3016,22 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>7.コマ表の表示</t>
+          <t>6.復元・初期設定</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>共通</t>
+          <t>室長</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>通常授業の並びを見る</t>
+          <t>読み込んだあと、生徒日程表・講師日程表のQRを見る</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>テンプレどおり毎週、いつもの曜日・時間に並んでいる</t>
+          <t>コピー元（本番）のQRは出ず、この教室が発行し直したQRになる（スキャンしても本番に書き込まれない）</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
@@ -3039,9 +3039,9 @@
           <t>★★★</t>
         </is>
       </c>
-      <c r="G62" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+      <c r="G62" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H62" s="6" t="n"/>
@@ -3053,32 +3053,32 @@
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>7.コマ表の表示</t>
+          <t>6.復元・初期設定</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>共通</t>
+          <t>室長</t>
         </is>
       </c>
       <c r="D63" s="8" t="inlineStr">
         <is>
-          <t>在籍期間外の週を見る</t>
+          <t>本番3教室（日大前/緑が丘/薬円台）で同じパネルを探す</t>
         </is>
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>入塾前・退塾後の生徒はその週に出ない</t>
+          <t>「他教室のバックアップをこの教室に読み込む」パネルは表示されない</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="G63" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="G63" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H63" s="6" t="n"/>
@@ -3088,7 +3088,7 @@
       <c r="A64" s="6" t="n">
         <v>61</v>
       </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>7.コマ表の表示</t>
         </is>
@@ -3100,17 +3100,17 @@
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>月の回数の上限があるか見る</t>
+          <t>コマ表を開く</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>「月◯回まで」の制限が無く、毎週配置される</t>
+          <t>曜日×時限の表が表示される</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★★</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr">
@@ -3137,17 +3137,17 @@
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>日曜（休校曜日）を見る</t>
+          <t>通常授業の並びを見る</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>コマ（席）が作られていない</t>
+          <t>テンプレどおり毎週、いつもの曜日・時間に並んでいる</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★★★</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr">
@@ -3174,12 +3174,12 @@
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>休みに設定した日を見る</t>
+          <t>在籍期間外の週を見る</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>コマが作られていない</t>
+          <t>入塾前・退塾後の生徒はその週に出ない</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>特別に開ける日（強制開校日）を見る</t>
+          <t>月の回数の上限があるか見る</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>休みの曜日でもその日はコマがある</t>
+          <t>「月◯回まで」の制限が無く、毎週配置される</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
@@ -3248,17 +3248,17 @@
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>祝日を見る</t>
+          <t>日曜（休校曜日）を見る</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>平日と同じように配置される（特別扱いしない）</t>
+          <t>コマ（席）が作られていない</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>1つのコマの中身を見る</t>
+          <t>休みに設定した日を見る</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>先生1人＋生徒は最大2人まで</t>
+          <t>コマが作られていない</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
@@ -3322,12 +3322,12 @@
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>時間の区切りと机の数を見る</t>
+          <t>特別に開ける日（強制開校日）を見る</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>1〜5限あり、机の数が教室設定どおり（標準14）</t>
+          <t>休みの曜日でもその日はコマがある</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
@@ -3359,12 +3359,12 @@
       </c>
       <c r="D71" s="8" t="inlineStr">
         <is>
-          <t>ペアの2人の科目・在籍を見る</t>
+          <t>祝日を見る</t>
         </is>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>2人がそれぞれ別の科目・別の在籍期間を持てる</t>
+          <t>平日と同じように配置される（特別扱いしない）</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>授業の種類の見分け方を見る</t>
+          <t>1つのコマの中身を見る</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>色分けは無く『通・振・講』などの文字で区別する</t>
+          <t>先生1人＋生徒は最大2人まで</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
@@ -3433,22 +3433,22 @@
       </c>
       <c r="D73" s="8" t="inlineStr">
         <is>
-          <t>手動で追加した生徒のセルを見る／ふれる</t>
+          <t>時間の区切りと机の数を見る</t>
         </is>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>セルの黄色背景は無く、ふれると『手動追加』とツールチップで分かる</t>
+          <t>1〜5限あり、机の数が教室設定どおり（標準14）</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="G73" s="10" t="inlineStr">
-        <is>
-          <t>更新</t>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H73" s="6" t="n"/>
@@ -3470,22 +3470,22 @@
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>生徒名が赤文字になっている席を探す</t>
+          <t>ペアの2人の科目・在籍を見る</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>赤文字は「出席不可コマに配置」または「講師が選ばれていない机に配置」のときだけ</t>
+          <t>2人がそれぞれ別の科目・別の在籍期間を持てる</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="G74" s="10" t="inlineStr">
-        <is>
-          <t>更新</t>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H74" s="6" t="n"/>
@@ -3507,12 +3507,12 @@
       </c>
       <c r="D75" s="8" t="inlineStr">
         <is>
-          <t>科目対応外・一コマ空け・制約違反などの席にふれる</t>
+          <t>授業の種類の見分け方を見る</t>
         </is>
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>名前は赤くならず、ツールチップで理由が読める</t>
+          <t>色分けは無く『通・振・講』などの文字で区別する</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
@@ -3520,9 +3520,9 @@
           <t>★★</t>
         </is>
       </c>
-      <c r="G75" s="10" t="inlineStr">
-        <is>
-          <t>更新</t>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H75" s="6" t="n"/>
@@ -3544,22 +3544,22 @@
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>授業時間（90/60/45分）の表示を見る</t>
+          <t>手動で追加した生徒のセルを見る／ふれる</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>設定された時間が表示される（未設定は90分扱い）</t>
+          <t>セルの黄色背景は無く、ふれると『手動追加』とツールチップで分かる</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="G76" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G76" s="10" t="inlineStr">
+        <is>
+          <t>更新</t>
         </is>
       </c>
       <c r="H76" s="6" t="n"/>
@@ -3581,22 +3581,22 @@
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>集団授業（集団理科／集団社会）の行を見る</t>
+          <t>生徒名が赤文字になっている席を探す</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>個別のコマとは別の行に表示される</t>
+          <t>赤文字は「出席不可コマに配置」または「講師が選ばれていない机に配置」のときだけ</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="G77" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G77" s="10" t="inlineStr">
+        <is>
+          <t>更新</t>
         </is>
       </c>
       <c r="H77" s="6" t="n"/>
@@ -3618,12 +3618,12 @@
       </c>
       <c r="D78" s="8" t="inlineStr">
         <is>
-          <t>「詰めて並び替え」を押す</t>
+          <t>科目対応外・一コマ空け・制約違反などの席にふれる</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>空席が詰まって並び替わり、出席・休みの記録が入った席が消えたりズレたりしない</t>
+          <t>名前は赤くならず、ツールチップで理由が読める</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
@@ -3631,9 +3631,9 @@
           <t>★★</t>
         </is>
       </c>
-      <c r="G78" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+      <c r="G78" s="10" t="inlineStr">
+        <is>
+          <t>更新</t>
         </is>
       </c>
       <c r="H78" s="6" t="n"/>
@@ -3643,9 +3643,9 @@
       <c r="A79" s="6" t="n">
         <v>76</v>
       </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>8.表示週の移動</t>
+      <c r="B79" s="8" t="inlineStr">
+        <is>
+          <t>7.コマ表の表示</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
@@ -3655,17 +3655,17 @@
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>「◀ 前週」「次週 ▶」を押す</t>
+          <t>授業時間（90/60/45分）の表示を見る</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>表示週が前後に移動する</t>
+          <t>設定された時間が表示される（未設定は90分扱い）</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>8.表示週の移動</t>
+          <t>7.コマ表の表示</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
@@ -3692,12 +3692,12 @@
       </c>
       <c r="D80" s="8" t="inlineStr">
         <is>
-          <t>「今日」を押す</t>
+          <t>集団授業（集団理科／集団社会）の行を見る</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>今日を含む週に戻る</t>
+          <t>個別のコマとは別の行に表示される</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
@@ -3705,9 +3705,9 @@
           <t>★</t>
         </is>
       </c>
-      <c r="G80" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+      <c r="G80" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H80" s="6" t="n"/>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>8.表示週の移動</t>
+          <t>7.コマ表の表示</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
@@ -3729,12 +3729,12 @@
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>「表示週を選択」を押す</t>
+          <t>「詰めて並び替え」を押す</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>アプリ自作のカレンダーが開く（端末の日付ピッカーではない）</t>
+          <t>空席が詰まって並び替わり、出席・休みの記録が入った席が消えたりズレたりしない</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
@@ -3754,7 +3754,7 @@
       <c r="A82" s="6" t="n">
         <v>79</v>
       </c>
-      <c r="B82" s="8" t="inlineStr">
+      <c r="B82" s="7" t="inlineStr">
         <is>
           <t>8.表示週の移動</t>
         </is>
@@ -3766,22 +3766,22 @@
       </c>
       <c r="D82" s="8" t="inlineStr">
         <is>
-          <t>カレンダーの ‹ › で月を送る</t>
+          <t>「◀ 前週」「次週 ▶」を押す</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>表示週は変わらない（月を見ているだけ）</t>
+          <t>表示週が前後に移動する</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="G82" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H82" s="6" t="n"/>
@@ -3803,22 +3803,22 @@
       </c>
       <c r="D83" s="8" t="inlineStr">
         <is>
-          <t>カレンダーの日付をタップする</t>
+          <t>「今日」を押す</t>
         </is>
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>そのとき初めてその日を含む週へ切り替わる</t>
+          <t>今日を含む週に戻る</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="G83" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H83" s="6" t="n"/>
@@ -3840,12 +3840,12 @@
       </c>
       <c r="D84" s="8" t="inlineStr">
         <is>
-          <t>カレンダーの外側をクリック／Escape／「閉じる」</t>
+          <t>「表示週を選択」を押す</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>表示週を変えずに閉じる</t>
+          <t>アプリ自作のカレンダーが開く（端末の日付ピッカーではない）</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
@@ -3877,17 +3877,17 @@
       </c>
       <c r="D85" s="8" t="inlineStr">
         <is>
-          <t>カレンダーの見た目を見る</t>
+          <t>カレンダーの ‹ › で月を送る</t>
         </is>
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>今日・選択中の週・前後の月がハイライトで区別できる</t>
+          <t>表示週は変わらない（月を見ているだけ）</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★★</t>
         </is>
       </c>
       <c r="G85" s="9" t="inlineStr">
@@ -3914,17 +3914,17 @@
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>カレンダー内の「今日」を押す</t>
+          <t>カレンダーの日付をタップする</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>今日の週へ移動する</t>
+          <t>そのとき初めてその日を含む週へ切り替わる</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★★</t>
         </is>
       </c>
       <c r="G86" s="9" t="inlineStr">
@@ -3939,9 +3939,9 @@
       <c r="A87" s="6" t="n">
         <v>84</v>
       </c>
-      <c r="B87" s="7" t="inlineStr">
-        <is>
-          <t>9.席の操作（生徒）</t>
+      <c r="B87" s="8" t="inlineStr">
+        <is>
+          <t>8.表示週の移動</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
@@ -3951,22 +3951,22 @@
       </c>
       <c r="D87" s="8" t="inlineStr">
         <is>
-          <t>生徒を同じコマ内の別の机へ動かす</t>
+          <t>カレンダーの外側をクリック／Escape／「閉じる」</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
         <is>
-          <t>その机に移り、元の机は空く（二重に残らない）</t>
+          <t>表示週を変えずに閉じる</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="G87" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G87" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H87" s="6" t="n"/>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>9.席の操作（生徒）</t>
+          <t>8.表示週の移動</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
@@ -3988,22 +3988,22 @@
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>生徒を別の曜日・時間の席へ動かす</t>
+          <t>カレンダーの見た目を見る</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>その曜日・時間に移る</t>
+          <t>今日・選択中の週・前後の月がハイライトで区別できる</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr">
         <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="G88" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G88" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H88" s="6" t="n"/>
@@ -4015,7 +4015,7 @@
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t>9.席の操作（生徒）</t>
+          <t>8.表示週の移動</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
@@ -4025,22 +4025,22 @@
       </c>
       <c r="D89" s="8" t="inlineStr">
         <is>
-          <t>すでに人が入っている席へ動かす</t>
+          <t>カレンダー内の「今日」を押す</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
         <is>
-          <t>2人が入れ替わる、または置けない（表が崩れない）</t>
+          <t>今日の週へ移動する</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="G89" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G89" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H89" s="6" t="n"/>
@@ -4050,7 +4050,7 @@
       <c r="A90" s="6" t="n">
         <v>87</v>
       </c>
-      <c r="B90" s="8" t="inlineStr">
+      <c r="B90" s="7" t="inlineStr">
         <is>
           <t>9.席の操作（生徒）</t>
         </is>
@@ -4062,17 +4062,17 @@
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>同じコマに同じ生徒を2回置こうとする</t>
+          <t>生徒を同じコマ内の別の机へ動かす</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>重複しては置けない（選んだ状態は残る）</t>
+          <t>その机に移り、元の机は空く（二重に残らない）</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★★★</t>
         </is>
       </c>
       <c r="G90" s="6" t="inlineStr">
@@ -4099,17 +4099,17 @@
       </c>
       <c r="D91" s="8" t="inlineStr">
         <is>
-          <t>生徒を持ち上げて同じ場所に戻す</t>
+          <t>生徒を別の曜日・時間の席へ動かす</t>
         </is>
       </c>
       <c r="E91" s="8" t="inlineStr">
         <is>
-          <t>何も変わらない</t>
+          <t>その曜日・時間に移る</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★★</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
@@ -4136,17 +4136,17 @@
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>通常授業を同じ日の別の席へ動かす</t>
+          <t>すでに人が入っている席へ動かす</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>通常のまま（種類が変わらず、移動の跡も残らない）</t>
+          <t>2人が入れ替わる、または置けない（表が崩れない）</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★★★</t>
         </is>
       </c>
       <c r="G92" s="6" t="inlineStr">
@@ -4173,12 +4173,12 @@
       </c>
       <c r="D93" s="8" t="inlineStr">
         <is>
-          <t>増えた授業（増コマ）を同じ日に動かす</t>
+          <t>同じコマに同じ生徒を2回置こうとする</t>
         </is>
       </c>
       <c r="E93" s="8" t="inlineStr">
         <is>
-          <t>通常授業に変わってしまわない</t>
+          <t>重複しては置けない（選んだ状態は残る）</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
@@ -4210,17 +4210,17 @@
       </c>
       <c r="D94" s="8" t="inlineStr">
         <is>
-          <t>振替を元の授業日の席へ戻す</t>
+          <t>生徒を持ち上げて同じ場所に戻す</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>通常授業として扱われる</t>
+          <t>何も変わらない</t>
         </is>
       </c>
       <c r="F94" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★</t>
         </is>
       </c>
       <c r="G94" s="6" t="inlineStr">
@@ -4247,12 +4247,12 @@
       </c>
       <c r="D95" s="8" t="inlineStr">
         <is>
-          <t>生徒名を長押し（約0.25秒）して掴む</t>
+          <t>通常授業を同じ日の別の席へ動かす</t>
         </is>
       </c>
       <c r="E95" s="8" t="inlineStr">
         <is>
-          <t>掴めて、盤面のマウスカーソルが「掴んでいる手」になる／画面周囲とドロップ先に青枠が出る</t>
+          <t>通常のまま（種類が変わらず、移動の跡も残らない）</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
@@ -4260,9 +4260,9 @@
           <t>★★</t>
         </is>
       </c>
-      <c r="G95" s="10" t="inlineStr">
-        <is>
-          <t>更新</t>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H95" s="6" t="n"/>
@@ -4284,12 +4284,12 @@
       </c>
       <c r="D96" s="8" t="inlineStr">
         <is>
-          <t>出席済みにした席へ別の生徒を配置・入れ替えしようとする</t>
+          <t>増えた授業（増コマ）を同じ日に動かす</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>配置できない（出席の記録が壊れない）</t>
+          <t>通常授業に変わってしまわない</t>
         </is>
       </c>
       <c r="F96" s="6" t="inlineStr">
@@ -4297,9 +4297,9 @@
           <t>★★</t>
         </is>
       </c>
-      <c r="G96" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H96" s="6" t="n"/>
@@ -4321,12 +4321,12 @@
       </c>
       <c r="D97" s="8" t="inlineStr">
         <is>
-          <t>「元に戻す」（↩アイコン）を押す</t>
+          <t>振替を元の授業日の席へ戻す</t>
         </is>
       </c>
       <c r="E97" s="8" t="inlineStr">
         <is>
-          <t>直前の操作が取り消される</t>
+          <t>通常授業として扱われる</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
@@ -4358,12 +4358,12 @@
       </c>
       <c r="D98" s="8" t="inlineStr">
         <is>
-          <t>「やり直し」（↪アイコン）を押す</t>
+          <t>生徒名を長押し（約0.25秒）して掴む</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>取り消した操作がやり直される</t>
+          <t>掴めて、盤面のマウスカーソルが「掴んでいる手」になる／画面周囲とドロップ先に青枠が出る</t>
         </is>
       </c>
       <c r="F98" s="6" t="inlineStr">
@@ -4371,9 +4371,9 @@
           <t>★★</t>
         </is>
       </c>
-      <c r="G98" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+      <c r="G98" s="10" t="inlineStr">
+        <is>
+          <t>更新</t>
         </is>
       </c>
       <c r="H98" s="6" t="n"/>
@@ -4383,9 +4383,9 @@
       <c r="A99" s="6" t="n">
         <v>96</v>
       </c>
-      <c r="B99" s="7" t="inlineStr">
-        <is>
-          <t>10.席の操作（講師）</t>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t>9.席の操作（生徒）</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
@@ -4395,12 +4395,12 @@
       </c>
       <c r="D99" s="8" t="inlineStr">
         <is>
-          <t>机の講師欄をクリックする</t>
+          <t>出席済みにした席へ別の生徒を配置・入れ替えしようとする</t>
         </is>
       </c>
       <c r="E99" s="8" t="inlineStr">
         <is>
-          <t>講師の選択肢が出る</t>
+          <t>配置できない（出席の記録が壊れない）</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
@@ -4408,9 +4408,9 @@
           <t>★★</t>
         </is>
       </c>
-      <c r="G99" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+      <c r="G99" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H99" s="6" t="n"/>
@@ -4422,7 +4422,7 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>10.席の操作（講師）</t>
+          <t>9.席の操作（生徒）</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>同じコマの他の机にすでに入っている講師を、選択肢から探す</t>
+          <t>「元に戻す」（↩アイコン）を押す</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>選択肢に出てこない（1人が同じコマで2つの机を持てない）</t>
+          <t>直前の操作が取り消される</t>
         </is>
       </c>
       <c r="F100" s="6" t="inlineStr">
@@ -4445,9 +4445,9 @@
           <t>★★</t>
         </is>
       </c>
-      <c r="G100" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H100" s="6" t="n"/>
@@ -4459,7 +4459,7 @@
       </c>
       <c r="B101" s="8" t="inlineStr">
         <is>
-          <t>10.席の操作（講師）</t>
+          <t>9.席の操作（生徒）</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
@@ -4469,22 +4469,22 @@
       </c>
       <c r="D101" s="8" t="inlineStr">
         <is>
-          <t>いま編集している机の現在の講師を、選択肢から探す</t>
+          <t>「やり直し」（↪アイコン）を押す</t>
         </is>
       </c>
       <c r="E101" s="8" t="inlineStr">
         <is>
-          <t>その講師は選択肢に残っている</t>
+          <t>取り消した操作がやり直される</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="G101" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G101" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H101" s="6" t="n"/>
@@ -4494,7 +4494,7 @@
       <c r="A102" s="6" t="n">
         <v>99</v>
       </c>
-      <c r="B102" s="8" t="inlineStr">
+      <c r="B102" s="7" t="inlineStr">
         <is>
           <t>10.席の操作（講師）</t>
         </is>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>講習期間内の日で、出席不可を提出済みの講師の選択肢を見る</t>
+          <t>机の講師欄をクリックする</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>名前の横に ○（出席可能）／×（出席不可）が付く</t>
+          <t>講師の選択肢が出る</t>
         </is>
       </c>
       <c r="F102" s="6" t="inlineStr">
@@ -4519,9 +4519,9 @@
           <t>★★</t>
         </is>
       </c>
-      <c r="G102" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H102" s="6" t="n"/>
@@ -4543,17 +4543,17 @@
       </c>
       <c r="D103" s="8" t="inlineStr">
         <is>
-          <t>未提出の講師／講習期間外の日で選択肢を見る</t>
+          <t>同じコマの他の机にすでに入っている講師を、選択肢から探す</t>
         </is>
       </c>
       <c r="E103" s="8" t="inlineStr">
         <is>
-          <t>記号は付かない</t>
+          <t>選択肢に出てこない（1人が同じコマで2つの机を持てない）</t>
         </is>
       </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="G103" s="9" t="inlineStr">
@@ -4580,17 +4580,17 @@
       </c>
       <c r="D104" s="8" t="inlineStr">
         <is>
-          <t>講師名を長押し（約0.25秒）して掴み、同じコマ内の空いている机へ落とす</t>
+          <t>いま編集している机の現在の講師を、選択肢から探す</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>その机へ講師が移る</t>
+          <t>その講師は選択肢に残っている</t>
         </is>
       </c>
       <c r="F104" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★</t>
         </is>
       </c>
       <c r="G104" s="9" t="inlineStr">
@@ -4617,12 +4617,12 @@
       </c>
       <c r="D105" s="8" t="inlineStr">
         <is>
-          <t>生徒がいない机どうしで講師をドロップする</t>
+          <t>講習期間内の日で、出席不可を提出済みの講師の選択肢を見る</t>
         </is>
       </c>
       <c r="E105" s="8" t="inlineStr">
         <is>
-          <t>2つの机の講師だけが入れ替わる</t>
+          <t>名前の横に ○（出席可能）／×（出席不可）が付く</t>
         </is>
       </c>
       <c r="F105" s="6" t="inlineStr">
@@ -4654,17 +4654,17 @@
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>生徒が入っている机へ講師をドロップする</t>
+          <t>未提出の講師／講習期間外の日で選択肢を見る</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>「講師だけ入れ替え」「席を入れ替え」を選ぶモーダルが左右に同じ色のボタンで出る</t>
+          <t>記号は付かない</t>
         </is>
       </c>
       <c r="F106" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★</t>
         </is>
       </c>
       <c r="G106" s="9" t="inlineStr">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="D107" s="8" t="inlineStr">
         <is>
-          <t>モーダルで「講師だけ入れ替え」を選ぶ</t>
+          <t>講師名を長押し（約0.25秒）して掴み、同じコマ内の空いている机へ落とす</t>
         </is>
       </c>
       <c r="E107" s="8" t="inlineStr">
         <is>
-          <t>生徒は動かず、講師だけが入れ替わる</t>
+          <t>その机へ講師が移る</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>モーダルで「席を入れ替え」を選ぶ</t>
+          <t>生徒がいない机どうしで講師をドロップする</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>講師と生徒のペアを保ったまま、席（机）ごと入れ替わる</t>
+          <t>2つの机の講師だけが入れ替わる</t>
         </is>
       </c>
       <c r="F108" s="6" t="inlineStr">
@@ -4765,17 +4765,17 @@
       </c>
       <c r="D109" s="8" t="inlineStr">
         <is>
-          <t>別のコマ（別の時限）の講師欄へドロップする</t>
+          <t>生徒が入っている机へ講師をドロップする</t>
         </is>
       </c>
       <c r="E109" s="8" t="inlineStr">
         <is>
-          <t>無効で何も起きない（同じコマ内だけ）</t>
+          <t>「講師だけ入れ替え」「席を入れ替え」を選ぶモーダルが左右に同じ色のボタンで出る</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="G109" s="9" t="inlineStr">
@@ -4802,17 +4802,17 @@
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>上の入れ替えをしたあと、講師日程表を開いて対象の生徒を探す</t>
+          <t>モーダルで「講師だけ入れ替え」を選ぶ</t>
         </is>
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>生徒は入れ替え後の講師のページにだけ出る（旧講師のページにも二重で出ない）</t>
+          <t>生徒は動かず、講師だけが入れ替わる</t>
         </is>
       </c>
       <c r="F110" s="6" t="inlineStr">
         <is>
-          <t>★★★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="G110" s="9" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="D111" s="8" t="inlineStr">
         <is>
-          <t>席の先生を消す／生徒を0人にする</t>
+          <t>モーダルで「席を入れ替え」を選ぶ</t>
         </is>
       </c>
       <c r="E111" s="8" t="inlineStr">
         <is>
-          <t>表示されていた先生の名前は消えずに残る</t>
+          <t>講師と生徒のペアを保ったまま、席（机）ごと入れ替わる</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr">
@@ -4852,9 +4852,9 @@
           <t>★★</t>
         </is>
       </c>
-      <c r="G111" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+      <c r="G111" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H111" s="6" t="n"/>
@@ -4876,17 +4876,17 @@
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>講師を削除したあと、ページを再読み込みする／別の週を見て戻る</t>
+          <t>別のコマ（別の時限）の講師欄へドロップする</t>
         </is>
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>消した講師が赤い状態で盤面に戻ってこない</t>
+          <t>無効で何も起きない（同じコマ内だけ）</t>
         </is>
       </c>
       <c r="F112" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★</t>
         </is>
       </c>
       <c r="G112" s="9" t="inlineStr">
@@ -4901,9 +4901,9 @@
       <c r="A113" s="6" t="n">
         <v>110</v>
       </c>
-      <c r="B113" s="7" t="inlineStr">
-        <is>
-          <t>11.休み・出席</t>
+      <c r="B113" s="8" t="inlineStr">
+        <is>
+          <t>10.席の操作（講師）</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="D113" s="8" t="inlineStr">
         <is>
-          <t>通常コマの生徒を「休み（欠席）」にする</t>
+          <t>上の入れ替えをしたあと、講師日程表を開いて対象の生徒を探す</t>
         </is>
       </c>
       <c r="E113" s="8" t="inlineStr">
         <is>
-          <t>振替が1コマ積まれ、コマは消えず『欠席』表示で残る</t>
+          <t>生徒は入れ替え後の講師のページにだけ出る（旧講師のページにも二重で出ない）</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr">
@@ -4926,9 +4926,9 @@
           <t>★★★</t>
         </is>
       </c>
-      <c r="G113" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+      <c r="G113" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H113" s="6" t="n"/>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>11.休み・出席</t>
+          <t>10.席の操作（講師）</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>欠席にした席をクリックする</t>
+          <t>席の先生を消す／生徒を0人にする</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>ロックされておらず、別生徒・体験・メモを足せる</t>
+          <t>表示されていた先生の名前は消えずに残る</t>
         </is>
       </c>
       <c r="F114" s="6" t="inlineStr">
@@ -4977,7 +4977,7 @@
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t>11.休み・出席</t>
+          <t>10.席の操作（講師）</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
@@ -4987,22 +4987,22 @@
       </c>
       <c r="D115" s="8" t="inlineStr">
         <is>
-          <t>「振無休（振替なしの休み）」を使う</t>
+          <t>講師を削除したあと、ページを再読み込みする／別の週を見て戻る</t>
         </is>
       </c>
       <c r="E115" s="8" t="inlineStr">
         <is>
-          <t>振替を増やさずに休みにできる</t>
+          <t>消した講師が赤い状態で盤面に戻ってこない</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr">
         <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="G115" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G115" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H115" s="6" t="n"/>
@@ -5012,7 +5012,7 @@
       <c r="A116" s="6" t="n">
         <v>113</v>
       </c>
-      <c r="B116" s="8" t="inlineStr">
+      <c r="B116" s="7" t="inlineStr">
         <is>
           <t>11.休み・出席</t>
         </is>
@@ -5024,17 +5024,17 @@
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>休みにした生徒を日程表で見る</t>
+          <t>通常コマの生徒を「休み（欠席）」にする</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>日程表に反映され、盤面では薄字</t>
+          <t>振替が1コマ積まれ、コマは消えず『欠席』表示で残る</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★★★</t>
         </is>
       </c>
       <c r="G116" s="6" t="inlineStr">
@@ -5061,12 +5061,12 @@
       </c>
       <c r="D117" s="8" t="inlineStr">
         <is>
-          <t>休みの席へ別の生徒を移動する</t>
+          <t>欠席にした席をクリックする</t>
         </is>
       </c>
       <c r="E117" s="8" t="inlineStr">
         <is>
-          <t>前の生徒の休みの日付を引き継がない</t>
+          <t>ロックされておらず、別生徒・体験・メモを足せる</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
@@ -5098,17 +5098,17 @@
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>生徒を「出席」にする</t>
+          <t>「振無休（振替なしの休み）」を使う</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>薄字になる</t>
+          <t>振替を増やさずに休みにできる</t>
         </is>
       </c>
       <c r="F118" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★</t>
         </is>
       </c>
       <c r="G118" s="6" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="D119" s="8" t="inlineStr">
         <is>
-          <t>出席にしたあと別画面へ移って戻る</t>
+          <t>休みにした生徒を日程表で見る</t>
         </is>
       </c>
       <c r="E119" s="8" t="inlineStr">
         <is>
-          <t>出席の状態が残っている</t>
+          <t>日程表に反映され、盤面では薄字</t>
         </is>
       </c>
       <c r="F119" s="6" t="inlineStr">
@@ -5172,22 +5172,22 @@
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>休み／出席を付けたあと解除する（休み解除・出席解除）</t>
+          <t>休みの席へ別の生徒を移動する</t>
         </is>
       </c>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>元に戻り、未消化の振替・講習の残数が二重に増えたり減ったりしない</t>
+          <t>前の生徒の休みの日付を引き継がない</t>
         </is>
       </c>
       <c r="F120" s="6" t="inlineStr">
         <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="G120" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G120" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H120" s="6" t="n"/>
@@ -5209,22 +5209,22 @@
       </c>
       <c r="D121" s="8" t="inlineStr">
         <is>
-          <t>盤面に配置済みの講習コマを欠席にし、そのあと欠席を解除する</t>
+          <t>生徒を「出席」にする</t>
         </is>
       </c>
       <c r="E121" s="8" t="inlineStr">
         <is>
-          <t>コマは盤面に残ったまま、未消化講習が増えない（二重計上しない）</t>
+          <t>薄字になる</t>
         </is>
       </c>
       <c r="F121" s="6" t="inlineStr">
         <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="G121" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G121" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H121" s="6" t="n"/>
@@ -5234,9 +5234,9 @@
       <c r="A122" s="6" t="n">
         <v>119</v>
       </c>
-      <c r="B122" s="7" t="inlineStr">
-        <is>
-          <t>12.振替ストック</t>
+      <c r="B122" s="8" t="inlineStr">
+        <is>
+          <t>11.休み・出席</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>日付をクリックして休日にする</t>
+          <t>出席にしたあと別画面へ移って戻る</t>
         </is>
       </c>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>その日に通常授業があった生徒が『休日振替』として自動で積まれる</t>
+          <t>出席の状態が残っている</t>
         </is>
       </c>
       <c r="F122" s="6" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t>12.振替ストック</t>
+          <t>11.休み・出席</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
@@ -5283,22 +5283,22 @@
       </c>
       <c r="D123" s="8" t="inlineStr">
         <is>
-          <t>未来の日付を休日にする</t>
+          <t>休み／出席を付けたあと解除する（休み解除・出席解除）</t>
         </is>
       </c>
       <c r="E123" s="8" t="inlineStr">
         <is>
-          <t>過ぎるのを待たず、その場ですぐ振替に計上される</t>
+          <t>元に戻り、未消化の振替・講習の残数が二重に増えたり減ったりしない</t>
         </is>
       </c>
       <c r="F123" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="G123" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="G123" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H123" s="6" t="n"/>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>12.振替ストック</t>
+          <t>11.休み・出席</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
@@ -5320,22 +5320,22 @@
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>休校曜日・強制開校日の扱いを見る</t>
+          <t>盤面に配置済みの講習コマを欠席にし、そのあと欠席を解除する</t>
         </is>
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>休校曜日由来は振替に積まれ、強制開校日は積まれない</t>
+          <t>コマは盤面に残ったまま、未消化講習が増えない（二重計上しない）</t>
         </is>
       </c>
       <c r="F124" s="6" t="inlineStr">
         <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="G124" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="G124" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H124" s="6" t="n"/>
@@ -5345,7 +5345,7 @@
       <c r="A125" s="6" t="n">
         <v>122</v>
       </c>
-      <c r="B125" s="8" t="inlineStr">
+      <c r="B125" s="7" t="inlineStr">
         <is>
           <t>12.振替ストック</t>
         </is>
@@ -5357,22 +5357,22 @@
       </c>
       <c r="D125" s="8" t="inlineStr">
         <is>
-          <t>出席済み・欠席済みの講習/振替が入っている日を、あとから休日に設定する</t>
+          <t>日付をクリックして休日にする</t>
         </is>
       </c>
       <c r="E125" s="8" t="inlineStr">
         <is>
-          <t>在庫（未消化）が二重に増えない・勝手に減らない</t>
+          <t>その日に通常授業があった生徒が『休日振替』として自動で積まれる</t>
         </is>
       </c>
       <c r="F125" s="6" t="inlineStr">
         <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="G125" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G125" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H125" s="6" t="n"/>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>振替ストックを空きコマに置く</t>
+          <t>未来の日付を休日にする</t>
         </is>
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>残りの数が1減る</t>
+          <t>過ぎるのを待たず、その場ですぐ振替に計上される</t>
         </is>
       </c>
       <c r="F126" s="6" t="inlineStr">
@@ -5431,17 +5431,17 @@
       </c>
       <c r="D127" s="8" t="inlineStr">
         <is>
-          <t>置いた振替を外す</t>
+          <t>休校曜日・強制開校日の扱いを見る</t>
         </is>
       </c>
       <c r="E127" s="8" t="inlineStr">
         <is>
-          <t>残りの数が1増える</t>
+          <t>休校曜日由来は振替に積まれ、強制開校日は積まれない</t>
         </is>
       </c>
       <c r="F127" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★</t>
         </is>
       </c>
       <c r="G127" s="6" t="inlineStr">
@@ -5468,17 +5468,17 @@
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>未消化振替の一覧から科目を選んで配置する</t>
+          <t>出席済み・欠席済みの講習/振替が入っている日を、あとから休日に設定する</t>
         </is>
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>選んだ科目のコマが置かれる（別の科目にならない）</t>
+          <t>在庫（未消化）が二重に増えない・勝手に減らない</t>
         </is>
       </c>
       <c r="F128" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★★★</t>
         </is>
       </c>
       <c r="G128" s="9" t="inlineStr">
@@ -5505,17 +5505,17 @@
       </c>
       <c r="D129" s="8" t="inlineStr">
         <is>
-          <t>コマを操作した後の振替パネルを見る</t>
+          <t>振替ストックを空きコマに置く</t>
         </is>
       </c>
       <c r="E129" s="8" t="inlineStr">
         <is>
-          <t>パネルが開いたまま維持される</t>
+          <t>残りの数が1減る</t>
         </is>
       </c>
       <c r="F129" s="6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="G129" s="6" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>手動追加した生徒の扱いを見る</t>
+          <t>置いた振替を外す</t>
         </is>
       </c>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>振替ストックには数えられない</t>
+          <t>残りの数が1増える</t>
         </is>
       </c>
       <c r="F130" s="6" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="D131" s="8" t="inlineStr">
         <is>
-          <t>同じコマに同じ生徒がいる状態で振替配置</t>
+          <t>未消化振替の一覧から科目を選んで配置する</t>
         </is>
       </c>
       <c r="E131" s="8" t="inlineStr">
         <is>
-          <t>拒否され、選んだ状態は残る</t>
+          <t>選んだ科目のコマが置かれる（別の科目にならない）</t>
         </is>
       </c>
       <c r="F131" s="6" t="inlineStr">
@@ -5592,9 +5592,9 @@
           <t>★★</t>
         </is>
       </c>
-      <c r="G131" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+      <c r="G131" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H131" s="6" t="n"/>
@@ -5616,12 +5616,12 @@
       </c>
       <c r="D132" s="8" t="inlineStr">
         <is>
-          <t>残数がマイナスになる操作を試す</t>
+          <t>コマを操作した後の振替パネルを見る</t>
         </is>
       </c>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>マイナスにならず0で止まる</t>
+          <t>パネルが開いたまま維持される</t>
         </is>
       </c>
       <c r="F132" s="6" t="inlineStr">
@@ -5641,9 +5641,9 @@
       <c r="A133" s="6" t="n">
         <v>130</v>
       </c>
-      <c r="B133" s="7" t="inlineStr">
-        <is>
-          <t>13.講習ストック</t>
+      <c r="B133" s="8" t="inlineStr">
+        <is>
+          <t>12.振替ストック</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="D133" s="8" t="inlineStr">
         <is>
-          <t>盤面操作だけで講習の希望数を増やそうとする</t>
+          <t>手動追加した生徒の扱いを見る</t>
         </is>
       </c>
       <c r="E133" s="8" t="inlineStr">
         <is>
-          <t>盤面では増やせない（増やすのはQR/日程表の提出だけ）</t>
+          <t>振替ストックには数えられない</t>
         </is>
       </c>
       <c r="F133" s="6" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t>13.講習ストック</t>
+          <t>12.振替ストック</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>盤面で講習コマを「空にする／削除」する</t>
+          <t>同じコマに同じ生徒がいる状態で振替配置</t>
         </is>
       </c>
       <c r="E134" s="8" t="inlineStr">
         <is>
-          <t>希望数が1減る</t>
+          <t>拒否され、選んだ状態は残る</t>
         </is>
       </c>
       <c r="F134" s="6" t="inlineStr">
@@ -5717,27 +5717,27 @@
       </c>
       <c r="B135" s="8" t="inlineStr">
         <is>
-          <t>13.講習ストック</t>
+          <t>12.振替ストック</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>室長</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="D135" s="8" t="inlineStr">
         <is>
-          <t>日程表で希望科目数を登録する</t>
+          <t>残数がマイナスになる操作を試す</t>
         </is>
       </c>
       <c r="E135" s="8" t="inlineStr">
         <is>
-          <t>自動配置されず、講習ストックに残る</t>
+          <t>マイナスにならず0で止まる</t>
         </is>
       </c>
       <c r="F135" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★</t>
         </is>
       </c>
       <c r="G135" s="6" t="inlineStr">
@@ -5752,7 +5752,7 @@
       <c r="A136" s="6" t="n">
         <v>133</v>
       </c>
-      <c r="B136" s="8" t="inlineStr">
+      <c r="B136" s="7" t="inlineStr">
         <is>
           <t>13.講習ストック</t>
         </is>
@@ -5764,17 +5764,17 @@
       </c>
       <c r="D136" s="8" t="inlineStr">
         <is>
-          <t>「通常授業のみ」の生徒を見る</t>
+          <t>盤面操作だけで講習の希望数を増やそうとする</t>
         </is>
       </c>
       <c r="E136" s="8" t="inlineStr">
         <is>
-          <t>講習ストックに数えられない</t>
+          <t>盤面では増やせない（増やすのはQR/日程表の提出だけ）</t>
         </is>
       </c>
       <c r="F136" s="6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="G136" s="6" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="D137" s="8" t="inlineStr">
         <is>
-          <t>ストックを選んで空欄に1コマ配置する</t>
+          <t>盤面で講習コマを「空にする／削除」する</t>
         </is>
       </c>
       <c r="E137" s="8" t="inlineStr">
         <is>
-          <t>配置される（希望数は減らず、未配置残が減る）</t>
+          <t>希望数が1減る</t>
         </is>
       </c>
       <c r="F137" s="6" t="inlineStr">
@@ -5833,27 +5833,27 @@
       </c>
       <c r="C138" s="6" t="inlineStr">
         <is>
-          <t>共通</t>
+          <t>室長</t>
         </is>
       </c>
       <c r="D138" s="8" t="inlineStr">
         <is>
-          <t>未消化講習の一覧で科目を選んでから配置する</t>
+          <t>日程表で希望科目数を登録する</t>
         </is>
       </c>
       <c r="E138" s="8" t="inlineStr">
         <is>
-          <t>選んだ科目が置かれる（先頭の科目に化けない。例：中3で数学を選んで英語が置かれない）</t>
+          <t>自動配置されず、講習ストックに残る</t>
         </is>
       </c>
       <c r="F138" s="6" t="inlineStr">
         <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="G138" s="10" t="inlineStr">
-        <is>
-          <t>更新</t>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G138" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H138" s="6" t="n"/>
@@ -5875,17 +5875,17 @@
       </c>
       <c r="D139" s="8" t="inlineStr">
         <is>
-          <t>講習を自動割振する</t>
+          <t>「通常授業のみ」の生徒を見る</t>
         </is>
       </c>
       <c r="E139" s="8" t="inlineStr">
         <is>
-          <t>条件に合う空きへ順に配置される</t>
+          <t>講習ストックに数えられない</t>
         </is>
       </c>
       <c r="F139" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★</t>
         </is>
       </c>
       <c r="G139" s="6" t="inlineStr">
@@ -5912,22 +5912,22 @@
       </c>
       <c r="D140" s="8" t="inlineStr">
         <is>
-          <t>自動割振で割り振りきれない残があった直後の画面を見る</t>
+          <t>ストックを選んで空欄に1コマ配置する</t>
         </is>
       </c>
       <c r="E140" s="8" t="inlineStr">
         <is>
-          <t>タップ配置モードに勝手に入らず、未消化一覧が開くだけ</t>
+          <t>配置される（希望数は減らず、未配置残が減る）</t>
         </is>
       </c>
       <c r="F140" s="6" t="inlineStr">
         <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="G140" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G140" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H140" s="6" t="n"/>
@@ -5949,22 +5949,22 @@
       </c>
       <c r="D141" s="8" t="inlineStr">
         <is>
-          <t>配置した講習を「ストックする（戻す）」</t>
+          <t>未消化講習の一覧で科目を選んでから配置する</t>
         </is>
       </c>
       <c r="E141" s="8" t="inlineStr">
         <is>
-          <t>未配置に戻る（希望数は変わらない）</t>
+          <t>選んだ科目が置かれる（先頭の科目に化けない。例：中3で数学を選んで英語が置かれない）</t>
         </is>
       </c>
       <c r="F141" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="G141" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="G141" s="10" t="inlineStr">
+        <is>
+          <t>更新</t>
         </is>
       </c>
       <c r="H141" s="6" t="n"/>
@@ -5986,12 +5986,12 @@
       </c>
       <c r="D142" s="8" t="inlineStr">
         <is>
-          <t>ストック由来の講習を「削除」する</t>
+          <t>講習を自動割振する</t>
         </is>
       </c>
       <c r="E142" s="8" t="inlineStr">
         <is>
-          <t>盤面から消え、未配置へは戻らず、希望数が1減る</t>
+          <t>条件に合う空きへ順に配置される</t>
         </is>
       </c>
       <c r="F142" s="6" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="D143" s="8" t="inlineStr">
         <is>
-          <t>手動追加した講習を削除する</t>
+          <t>自動割振で割り振りきれない残があった直後の画面を見る</t>
         </is>
       </c>
       <c r="E143" s="8" t="inlineStr">
         <is>
-          <t>削除でき、希望数は変わらない（戻しはできない）</t>
+          <t>タップ配置モードに勝手に入らず、未消化一覧が開くだけ</t>
         </is>
       </c>
       <c r="F143" s="6" t="inlineStr">
@@ -6036,9 +6036,9 @@
           <t>★</t>
         </is>
       </c>
-      <c r="G143" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+      <c r="G143" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H143" s="6" t="n"/>
@@ -6060,17 +6060,17 @@
       </c>
       <c r="D144" s="8" t="inlineStr">
         <is>
-          <t>講習コマを直接編集しようとする</t>
+          <t>配置した講習を「ストックする（戻す）」</t>
         </is>
       </c>
       <c r="E144" s="8" t="inlineStr">
         <is>
-          <t>直接編集の機能は無い（削除→追加し直しで対応）</t>
+          <t>未配置に戻る（希望数は変わらない）</t>
         </is>
       </c>
       <c r="F144" s="6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="G144" s="6" t="inlineStr">
@@ -6097,17 +6097,17 @@
       </c>
       <c r="D145" s="8" t="inlineStr">
         <is>
-          <t>講習を手動追加するとき授業時間を選ぶ</t>
+          <t>ストック由来の講習を「削除」する</t>
         </is>
       </c>
       <c r="E145" s="8" t="inlineStr">
         <is>
-          <t>90/60/45分を選べる（未選択は90）</t>
+          <t>盤面から消え、未配置へは戻らず、希望数が1減る</t>
         </is>
       </c>
       <c r="F145" s="6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="G145" s="6" t="inlineStr">
@@ -6129,17 +6129,17 @@
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
-          <t>室長</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="D146" s="8" t="inlineStr">
         <is>
-          <t>日程表で講習の登録を解除する</t>
+          <t>手動追加した講習を削除する</t>
         </is>
       </c>
       <c r="E146" s="8" t="inlineStr">
         <is>
-          <t>その期間の講習コマが盤面から外れる</t>
+          <t>削除でき、希望数は変わらない（戻しはできない）</t>
         </is>
       </c>
       <c r="F146" s="6" t="inlineStr">
@@ -6166,17 +6166,17 @@
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>室長</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="D147" s="8" t="inlineStr">
         <is>
-          <t>解除した講習を再登録する</t>
+          <t>講習コマを直接編集しようとする</t>
         </is>
       </c>
       <c r="E147" s="8" t="inlineStr">
         <is>
-          <t>消費した分も戻して、希望数と合うストックに再計算される</t>
+          <t>直接編集の機能は無い（削除→追加し直しで対応）</t>
         </is>
       </c>
       <c r="F147" s="6" t="inlineStr">
@@ -6203,17 +6203,17 @@
       </c>
       <c r="C148" s="6" t="inlineStr">
         <is>
-          <t>室長</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="D148" s="8" t="inlineStr">
         <is>
-          <t>講師日程表で講習の登録を解除する</t>
+          <t>講習を手動追加するとき授業時間を選ぶ</t>
         </is>
       </c>
       <c r="E148" s="8" t="inlineStr">
         <is>
-          <t>その講師だけ外れ、生徒の講習予定は残る</t>
+          <t>90/60/45分を選べる（未選択は90）</t>
         </is>
       </c>
       <c r="F148" s="6" t="inlineStr">
@@ -6245,22 +6245,22 @@
       </c>
       <c r="D149" s="8" t="inlineStr">
         <is>
-          <t>講習を配置したあと、基本データでその生徒の名前を変更する</t>
+          <t>日程表で講習の登録を解除する</t>
         </is>
       </c>
       <c r="E149" s="8" t="inlineStr">
         <is>
-          <t>未消化講習の残数が壊れない（改名しても配置と残数の対応が保たれる）</t>
+          <t>その期間の講習コマが盤面から外れる</t>
         </is>
       </c>
       <c r="F149" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="G149" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G149" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H149" s="6" t="n"/>
@@ -6270,9 +6270,9 @@
       <c r="A150" s="6" t="n">
         <v>147</v>
       </c>
-      <c r="B150" s="7" t="inlineStr">
-        <is>
-          <t>14.基本データ</t>
+      <c r="B150" s="8" t="inlineStr">
+        <is>
+          <t>13.講習ストック</t>
         </is>
       </c>
       <c r="C150" s="6" t="inlineStr">
@@ -6282,17 +6282,17 @@
       </c>
       <c r="D150" s="8" t="inlineStr">
         <is>
-          <t>基本データのタブを見る</t>
+          <t>解除した講習を再登録する</t>
         </is>
       </c>
       <c r="E150" s="8" t="inlineStr">
         <is>
-          <t>生徒／講師／教室データの3つ（マネージャータブは無い）</t>
+          <t>消費した分も戻して、希望数と合うストックに再計算される</t>
         </is>
       </c>
       <c r="F150" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★</t>
         </is>
       </c>
       <c r="G150" s="6" t="inlineStr">
@@ -6309,7 +6309,7 @@
       </c>
       <c r="B151" s="8" t="inlineStr">
         <is>
-          <t>14.基本データ</t>
+          <t>13.講習ストック</t>
         </is>
       </c>
       <c r="C151" s="6" t="inlineStr">
@@ -6319,12 +6319,12 @@
       </c>
       <c r="D151" s="8" t="inlineStr">
         <is>
-          <t>表の並び替え・フィルタを使う（生徒・講師タブ）</t>
+          <t>講師日程表で講習の登録を解除する</t>
         </is>
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>並び替え・絞り込みができる</t>
+          <t>その講師だけ外れ、生徒の講習予定は残る</t>
         </is>
       </c>
       <c r="F151" s="6" t="inlineStr">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
-          <t>14.基本データ</t>
+          <t>13.講習ストック</t>
         </is>
       </c>
       <c r="C152" s="6" t="inlineStr">
@@ -6356,22 +6356,22 @@
       </c>
       <c r="D152" s="8" t="inlineStr">
         <is>
-          <t>生徒の入力項目を見る</t>
+          <t>講習を配置したあと、基本データでその生徒の名前を変更する</t>
         </is>
       </c>
       <c r="E152" s="8" t="inlineStr">
         <is>
-          <t>名前・表示名・メール・入塾日・退塾日・生年月日（非表示項目は無い）</t>
+          <t>未消化講習の残数が壊れない（改名しても配置と残数の対応が保たれる）</t>
         </is>
       </c>
       <c r="F152" s="6" t="inlineStr">
         <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="G152" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G152" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H152" s="6" t="n"/>
@@ -6381,7 +6381,7 @@
       <c r="A153" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="B153" s="8" t="inlineStr">
+      <c r="B153" s="7" t="inlineStr">
         <is>
           <t>14.基本データ</t>
         </is>
@@ -6393,17 +6393,17 @@
       </c>
       <c r="D153" s="8" t="inlineStr">
         <is>
-          <t>生徒の学年欄を探す</t>
+          <t>基本データのタブを見る</t>
         </is>
       </c>
       <c r="E153" s="8" t="inlineStr">
         <is>
-          <t>学年欄は無く、生年月日から自動で判定される</t>
+          <t>生徒／講師／教室データの3つ（マネージャータブは無い）</t>
         </is>
       </c>
       <c r="F153" s="6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="G153" s="6" t="inlineStr">
@@ -6430,22 +6430,22 @@
       </c>
       <c r="D154" s="8" t="inlineStr">
         <is>
-          <t>入塾日が未来の生徒を基本データの名簿で見る</t>
+          <t>表の並び替え・フィルタを使う（生徒・講師タブ）</t>
         </is>
       </c>
       <c r="E154" s="8" t="inlineStr">
         <is>
-          <t>在籍として名簿に表示される（この画面だけ入塾日を問わない）</t>
+          <t>並び替え・絞り込みができる</t>
         </is>
       </c>
       <c r="F154" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="G154" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G154" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H154" s="6" t="n"/>
@@ -6467,22 +6467,22 @@
       </c>
       <c r="D155" s="8" t="inlineStr">
         <is>
-          <t>退塾日当日／翌日の生徒を基本データの名簿で見る</t>
+          <t>生徒の入力項目を見る</t>
         </is>
       </c>
       <c r="E155" s="8" t="inlineStr">
         <is>
-          <t>当日は在籍、翌日から非在籍として表示される</t>
+          <t>名前・表示名・メール・入塾日・退塾日・生年月日（非表示項目は無い）</t>
         </is>
       </c>
       <c r="F155" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="G155" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G155" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H155" s="6" t="n"/>
@@ -6504,12 +6504,12 @@
       </c>
       <c r="D156" s="8" t="inlineStr">
         <is>
-          <t>高3の生徒を基本データの名簿で見る</t>
+          <t>生徒の学年欄を探す</t>
         </is>
       </c>
       <c r="E156" s="8" t="inlineStr">
         <is>
-          <t>卒業日（翌3/31）が退塾日として自動補完され、以降は非在籍表示になる</t>
+          <t>学年欄は無く、生年月日から自動で判定される</t>
         </is>
       </c>
       <c r="F156" s="6" t="inlineStr">
@@ -6517,9 +6517,9 @@
           <t>★</t>
         </is>
       </c>
-      <c r="G156" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+      <c r="G156" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H156" s="6" t="n"/>
@@ -6541,12 +6541,12 @@
       </c>
       <c r="D157" s="8" t="inlineStr">
         <is>
-          <t>上の生徒たちを盤面・日程表で見る</t>
+          <t>入塾日が未来の生徒を基本データの名簿で見る</t>
         </is>
       </c>
       <c r="E157" s="8" t="inlineStr">
         <is>
-          <t>盤面・日程表・集計は従来どおり（入塾日前・卒業後は出ない）＝管理画面の表示だけが違う</t>
+          <t>在籍として名簿に表示される（この画面だけ入塾日を問わない）</t>
         </is>
       </c>
       <c r="F157" s="6" t="inlineStr">
@@ -6578,22 +6578,22 @@
       </c>
       <c r="D158" s="8" t="inlineStr">
         <is>
-          <t>講師の入力項目を見る</t>
+          <t>退塾日当日／翌日の生徒を基本データの名簿で見る</t>
         </is>
       </c>
       <c r="E158" s="8" t="inlineStr">
         <is>
-          <t>氏名・表示名・メール・入塾日・退塾日・担当科目（出勤コマ/メモ/非表示は無い）</t>
+          <t>当日は在籍、翌日から非在籍として表示される</t>
         </is>
       </c>
       <c r="F158" s="6" t="inlineStr">
         <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="G158" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G158" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H158" s="6" t="n"/>
@@ -6615,12 +6615,12 @@
       </c>
       <c r="D159" s="8" t="inlineStr">
         <is>
-          <t>講師を一時的に隠したいとき</t>
+          <t>高3の生徒を基本データの名簿で見る</t>
         </is>
       </c>
       <c r="E159" s="8" t="inlineStr">
         <is>
-          <t>退塾日を入れて代用できる（戻すと復帰）</t>
+          <t>卒業日（翌3/31）が退塾日として自動補完され、以降は非在籍表示になる</t>
         </is>
       </c>
       <c r="F159" s="6" t="inlineStr">
@@ -6628,9 +6628,9 @@
           <t>★</t>
         </is>
       </c>
-      <c r="G159" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+      <c r="G159" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H159" s="6" t="n"/>
@@ -6652,22 +6652,22 @@
       </c>
       <c r="D160" s="8" t="inlineStr">
         <is>
-          <t>講師の担当科目と学年を見る</t>
+          <t>上の生徒たちを盤面・日程表で見る</t>
         </is>
       </c>
       <c r="E160" s="8" t="inlineStr">
         <is>
-          <t>選んだ学年以下を担当できる設定になっている</t>
+          <t>盤面・日程表・集計は従来どおり（入塾日前・卒業後は出ない）＝管理画面の表示だけが違う</t>
         </is>
       </c>
       <c r="F160" s="6" t="inlineStr">
         <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="G160" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G160" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H160" s="6" t="n"/>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="D161" s="8" t="inlineStr">
         <is>
-          <t>在籍／非在籍の講師の表示切替を使う</t>
+          <t>講師の入力項目を見る</t>
         </is>
       </c>
       <c r="E161" s="8" t="inlineStr">
         <is>
-          <t>切り替えて表示できる</t>
+          <t>氏名・表示名・メール・入塾日・退塾日・担当科目（出勤コマ/メモ/非表示は無い）</t>
         </is>
       </c>
       <c r="F161" s="6" t="inlineStr">
@@ -6726,17 +6726,17 @@
       </c>
       <c r="D162" s="8" t="inlineStr">
         <is>
-          <t>教室データタブを開く</t>
+          <t>講師を一時的に隠したいとき</t>
         </is>
       </c>
       <c r="E162" s="8" t="inlineStr">
         <is>
-          <t>定休日（休校曜日）と机数を後から変更できる</t>
+          <t>退塾日を入れて代用できる（戻すと復帰）</t>
         </is>
       </c>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★</t>
         </is>
       </c>
       <c r="G162" s="6" t="inlineStr">
@@ -6763,12 +6763,12 @@
       </c>
       <c r="D163" s="8" t="inlineStr">
         <is>
-          <t>通常授業の編集タブを探す</t>
+          <t>講師の担当科目と学年を見る</t>
         </is>
       </c>
       <c r="E163" s="8" t="inlineStr">
         <is>
-          <t>基本データには無い（通常授業はコマ表のテンプレで編集）</t>
+          <t>選んだ学年以下を担当できる設定になっている</t>
         </is>
       </c>
       <c r="F163" s="6" t="inlineStr">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="D164" s="8" t="inlineStr">
         <is>
-          <t>祝日・強制開校日の編集を探す</t>
+          <t>在籍／非在籍の講師の表示切替を使う</t>
         </is>
       </c>
       <c r="E164" s="8" t="inlineStr">
         <is>
-          <t>基本データには無い（盤面で設定する）</t>
+          <t>切り替えて表示できる</t>
         </is>
       </c>
       <c r="F164" s="6" t="inlineStr">
@@ -6837,17 +6837,17 @@
       </c>
       <c r="D165" s="8" t="inlineStr">
         <is>
-          <t>生徒を追加・編集する</t>
+          <t>教室データタブを開く</t>
         </is>
       </c>
       <c r="E165" s="8" t="inlineStr">
         <is>
-          <t>保存後も反映が残る</t>
+          <t>定休日（休校曜日）と机数を後から変更できる</t>
         </is>
       </c>
       <c r="F165" s="6" t="inlineStr">
         <is>
-          <t>★★★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="G165" s="6" t="inlineStr">
@@ -6874,22 +6874,22 @@
       </c>
       <c r="D166" s="8" t="inlineStr">
         <is>
-          <t>生徒の「削除」を押す</t>
+          <t>通常授業の編集タブを探す</t>
         </is>
       </c>
       <c r="E166" s="8" t="inlineStr">
         <is>
-          <t>確認モーダルが出る（元に戻せない旨・データを残すなら退塾日で非表示にできる案内。本番ではパスワード再認証も要求）</t>
+          <t>基本データには無い（通常授業はコマ表のテンプレで編集）</t>
         </is>
       </c>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="G166" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G166" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H166" s="6" t="n"/>
@@ -6911,22 +6911,22 @@
       </c>
       <c r="D167" s="8" t="inlineStr">
         <is>
-          <t>未消化の講習／振替が残っている生徒を削除しようとする</t>
+          <t>祝日・強制開校日の編集を探す</t>
         </is>
       </c>
       <c r="E167" s="8" t="inlineStr">
         <is>
-          <t>残っている数が警告として表示される</t>
+          <t>基本データには無い（盤面で設定する）</t>
         </is>
       </c>
       <c r="F167" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="G167" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G167" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H167" s="6" t="n"/>
@@ -6948,17 +6948,17 @@
       </c>
       <c r="D168" s="8" t="inlineStr">
         <is>
-          <t>講師を追加・編集・削除する</t>
+          <t>生徒を追加・編集する</t>
         </is>
       </c>
       <c r="E168" s="8" t="inlineStr">
         <is>
-          <t>保存後も反映が残る（削除は同じ確認モーダル）</t>
+          <t>保存後も反映が残る</t>
         </is>
       </c>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★★★</t>
         </is>
       </c>
       <c r="G168" s="6" t="inlineStr">
@@ -6985,22 +6985,22 @@
       </c>
       <c r="D169" s="8" t="inlineStr">
         <is>
-          <t>Excelのテンプレート出力／現データ出力をする</t>
+          <t>生徒の「削除」を押す</t>
         </is>
       </c>
       <c r="E169" s="8" t="inlineStr">
         <is>
-          <t>出力できる</t>
+          <t>確認モーダルが出る（元に戻せない旨・データを残すなら退塾日で非表示にできる案内。本番ではパスワード再認証も要求）</t>
         </is>
       </c>
       <c r="F169" s="6" t="inlineStr">
         <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="G169" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="G169" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H169" s="6" t="n"/>
@@ -7022,22 +7022,22 @@
       </c>
       <c r="D170" s="8" t="inlineStr">
         <is>
-          <t>ID列を残してExcelを差分取込する</t>
+          <t>未消化の講習／振替が残っている生徒を削除しようとする</t>
         </is>
       </c>
       <c r="E170" s="8" t="inlineStr">
         <is>
-          <t>講習・ルール・盤面・ストックを保ったまま更新される</t>
+          <t>残っている数が警告として表示される</t>
         </is>
       </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="G170" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G170" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H170" s="6" t="n"/>
@@ -7059,17 +7059,17 @@
       </c>
       <c r="D171" s="8" t="inlineStr">
         <is>
-          <t>おかしいデータをExcel取込する</t>
+          <t>講師を追加・編集・削除する</t>
         </is>
       </c>
       <c r="E171" s="8" t="inlineStr">
         <is>
-          <t>エラーとして弾かれる</t>
+          <t>保存後も反映が残る（削除は同じ確認モーダル）</t>
         </is>
       </c>
       <c r="F171" s="6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="G171" s="6" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="D172" s="8" t="inlineStr">
         <is>
-          <t>小学生の科目選択を見る</t>
+          <t>Excelのテンプレート出力／現データ出力をする</t>
         </is>
       </c>
       <c r="E172" s="8" t="inlineStr">
         <is>
-          <t>合体科目「理社」が選べる（算国と同じ扱い）</t>
+          <t>出力できる</t>
         </is>
       </c>
       <c r="F172" s="6" t="inlineStr">
@@ -7109,9 +7109,9 @@
           <t>★</t>
         </is>
       </c>
-      <c r="G172" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+      <c r="G172" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H172" s="6" t="n"/>
@@ -7133,12 +7133,12 @@
       </c>
       <c r="D173" s="8" t="inlineStr">
         <is>
-          <t>中学生以上の科目選択を見る</t>
+          <t>ID列を残してExcelを差分取込する</t>
         </is>
       </c>
       <c r="E173" s="8" t="inlineStr">
         <is>
-          <t>「理社」は出ない（小学限定）</t>
+          <t>講習・ルール・盤面・ストックを保ったまま更新される</t>
         </is>
       </c>
       <c r="F173" s="6" t="inlineStr">
@@ -7146,9 +7146,9 @@
           <t>★</t>
         </is>
       </c>
-      <c r="G173" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+      <c r="G173" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H173" s="6" t="n"/>
@@ -7158,9 +7158,9 @@
       <c r="A174" s="6" t="n">
         <v>171</v>
       </c>
-      <c r="B174" s="7" t="inlineStr">
-        <is>
-          <t>15.特別講習データ</t>
+      <c r="B174" s="8" t="inlineStr">
+        <is>
+          <t>14.基本データ</t>
         </is>
       </c>
       <c r="C174" s="6" t="inlineStr">
@@ -7170,17 +7170,17 @@
       </c>
       <c r="D174" s="8" t="inlineStr">
         <is>
-          <t>特別講習データ画面で講習名＋期間を登録する</t>
+          <t>おかしいデータをExcel取込する</t>
         </is>
       </c>
       <c r="E174" s="8" t="inlineStr">
         <is>
-          <t>登録でき、一覧から編集・削除できる</t>
+          <t>エラーとして弾かれる</t>
         </is>
       </c>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★</t>
         </is>
       </c>
       <c r="G174" s="6" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="B175" s="8" t="inlineStr">
         <is>
-          <t>15.特別講習データ</t>
+          <t>14.基本データ</t>
         </is>
       </c>
       <c r="C175" s="6" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="D175" s="8" t="inlineStr">
         <is>
-          <t>新規教室の特別講習データを見る</t>
+          <t>小学生の科目選択を見る</t>
         </is>
       </c>
       <c r="E175" s="8" t="inlineStr">
         <is>
-          <t>空の状態で始まる（過去サンプルが無い）</t>
+          <t>合体科目「理社」が選べる（算国と同じ扱い）</t>
         </is>
       </c>
       <c r="F175" s="6" t="inlineStr">
@@ -7220,9 +7220,9 @@
           <t>★</t>
         </is>
       </c>
-      <c r="G175" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+      <c r="G175" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H175" s="6" t="n"/>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="B176" s="8" t="inlineStr">
         <is>
-          <t>15.特別講習データ</t>
+          <t>14.基本データ</t>
         </is>
       </c>
       <c r="C176" s="6" t="inlineStr">
@@ -7244,12 +7244,12 @@
       </c>
       <c r="D176" s="8" t="inlineStr">
         <is>
-          <t>期間が重なる講習をもう1件作ろうとする</t>
+          <t>中学生以上の科目選択を見る</t>
         </is>
       </c>
       <c r="E176" s="8" t="inlineStr">
         <is>
-          <t>重複した期間では作れない</t>
+          <t>「理社」は出ない（小学限定）</t>
         </is>
       </c>
       <c r="F176" s="6" t="inlineStr">
@@ -7269,7 +7269,7 @@
       <c r="A177" s="6" t="n">
         <v>174</v>
       </c>
-      <c r="B177" s="8" t="inlineStr">
+      <c r="B177" s="7" t="inlineStr">
         <is>
           <t>15.特別講習データ</t>
         </is>
@@ -7281,17 +7281,17 @@
       </c>
       <c r="D177" s="8" t="inlineStr">
         <is>
-          <t>欠席不可・希望の登録経路を見る</t>
+          <t>特別講習データ画面で講習名＋期間を登録する</t>
         </is>
       </c>
       <c r="E177" s="8" t="inlineStr">
         <is>
-          <t>日程表に一本化（コマ表クリック→別タブ入力の経路が無い）</t>
+          <t>登録でき、一覧から編集・削除できる</t>
         </is>
       </c>
       <c r="F177" s="6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="G177" s="6" t="inlineStr">
@@ -7318,12 +7318,12 @@
       </c>
       <c r="D178" s="8" t="inlineStr">
         <is>
-          <t>講習編集パネルの案内文を読む</t>
+          <t>新規教室の特別講習データを見る</t>
         </is>
       </c>
       <c r="E178" s="8" t="inlineStr">
         <is>
-          <t>日程表／QRの案内になっている（「別タブで開きます」という古い案内が無い）</t>
+          <t>空の状態で始まる（過去サンプルが無い）</t>
         </is>
       </c>
       <c r="F178" s="6" t="inlineStr">
@@ -7331,9 +7331,9 @@
           <t>★</t>
         </is>
       </c>
-      <c r="G178" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+      <c r="G178" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H178" s="6" t="n"/>
@@ -7355,22 +7355,22 @@
       </c>
       <c r="D179" s="8" t="inlineStr">
         <is>
-          <t>生徒・講師の個別QRリンクを発行する</t>
+          <t>期間が重なる講習をもう1件作ろうとする</t>
         </is>
       </c>
       <c r="E179" s="8" t="inlineStr">
         <is>
-          <t>それぞれにQR（提出リンク）を発行できる</t>
+          <t>重複した期間では作れない</t>
         </is>
       </c>
       <c r="F179" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="G179" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G179" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H179" s="6" t="n"/>
@@ -7392,12 +7392,12 @@
       </c>
       <c r="D180" s="8" t="inlineStr">
         <is>
-          <t>提出が来たときの画面を見る</t>
+          <t>欠席不可・希望の登録経路を見る</t>
         </is>
       </c>
       <c r="E180" s="8" t="inlineStr">
         <is>
-          <t>室長側にリアルタイムで届く</t>
+          <t>日程表に一本化（コマ表クリック→別タブ入力の経路が無い）</t>
         </is>
       </c>
       <c r="F180" s="6" t="inlineStr">
@@ -7417,34 +7417,34 @@
       <c r="A181" s="6" t="n">
         <v>178</v>
       </c>
-      <c r="B181" s="7" t="inlineStr">
-        <is>
-          <t>16.QR提出（保護者・生徒）</t>
+      <c r="B181" s="8" t="inlineStr">
+        <is>
+          <t>15.特別講習データ</t>
         </is>
       </c>
       <c r="C181" s="6" t="inlineStr">
         <is>
-          <t>提出</t>
+          <t>室長</t>
         </is>
       </c>
       <c r="D181" s="8" t="inlineStr">
         <is>
-          <t>QRリンクを開く</t>
+          <t>講習編集パネルの案内文を読む</t>
         </is>
       </c>
       <c r="E181" s="8" t="inlineStr">
         <is>
-          <t>本人用フォーム（講習名・氏名・期間）が表示される</t>
+          <t>日程表／QRの案内になっている（「別タブで開きます」という古い案内が無い）</t>
         </is>
       </c>
       <c r="F181" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="G181" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G181" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H181" s="6" t="n"/>
@@ -7456,22 +7456,22 @@
       </c>
       <c r="B182" s="8" t="inlineStr">
         <is>
-          <t>16.QR提出（保護者・生徒）</t>
+          <t>15.特別講習データ</t>
         </is>
       </c>
       <c r="C182" s="6" t="inlineStr">
         <is>
-          <t>提出</t>
+          <t>室長</t>
         </is>
       </c>
       <c r="D182" s="8" t="inlineStr">
         <is>
-          <t>出席できないコマをタップする</t>
+          <t>生徒・講師の個別QRリンクを発行する</t>
         </is>
       </c>
       <c r="E182" s="8" t="inlineStr">
         <is>
-          <t>×が付く</t>
+          <t>それぞれにQR（提出リンク）を発行できる</t>
         </is>
       </c>
       <c r="F182" s="6" t="inlineStr">
@@ -7493,22 +7493,22 @@
       </c>
       <c r="B183" s="8" t="inlineStr">
         <is>
-          <t>16.QR提出（保護者・生徒）</t>
+          <t>15.特別講習データ</t>
         </is>
       </c>
       <c r="C183" s="6" t="inlineStr">
         <is>
-          <t>提出</t>
+          <t>室長</t>
         </is>
       </c>
       <c r="D183" s="8" t="inlineStr">
         <is>
-          <t>日付や限のヘッダをタップする</t>
+          <t>提出が来たときの画面を見る</t>
         </is>
       </c>
       <c r="E183" s="8" t="inlineStr">
         <is>
-          <t>日付タップで終日不可、限タップでその列全部が不可になる</t>
+          <t>室長側にリアルタイムで届く</t>
         </is>
       </c>
       <c r="F183" s="6" t="inlineStr">
@@ -7528,7 +7528,7 @@
       <c r="A184" s="6" t="n">
         <v>181</v>
       </c>
-      <c r="B184" s="8" t="inlineStr">
+      <c r="B184" s="7" t="inlineStr">
         <is>
           <t>16.QR提出（保護者・生徒）</t>
         </is>
@@ -7540,12 +7540,12 @@
       </c>
       <c r="D184" s="8" t="inlineStr">
         <is>
-          <t>すでに盤面に割り振られているコマを見る</t>
+          <t>QRリンクを開く</t>
         </is>
       </c>
       <c r="E184" s="8" t="inlineStr">
         <is>
-          <t>青く表示され、そこには「講数」「通英」「振国」のように種別＋科目が出る</t>
+          <t>本人用フォーム（講習名・氏名・期間）が表示される</t>
         </is>
       </c>
       <c r="F184" s="6" t="inlineStr">
@@ -7553,9 +7553,9 @@
           <t>★★</t>
         </is>
       </c>
-      <c r="G184" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+      <c r="G184" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H184" s="6" t="n"/>
@@ -7577,17 +7577,17 @@
       </c>
       <c r="D185" s="8" t="inlineStr">
         <is>
-          <t>すでに盤面にあるコマを不可にしようとする</t>
+          <t>出席できないコマをタップする</t>
         </is>
       </c>
       <c r="E185" s="8" t="inlineStr">
         <is>
-          <t>確認が出る</t>
+          <t>×が付く</t>
         </is>
       </c>
       <c r="F185" s="6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="G185" s="6" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="D186" s="8" t="inlineStr">
         <is>
-          <t>休校日のマスを見る</t>
+          <t>日付や限のヘッダをタップする</t>
         </is>
       </c>
       <c r="E186" s="8" t="inlineStr">
         <is>
-          <t>灰色で選べない</t>
+          <t>日付タップで終日不可、限タップでその列全部が不可になる</t>
         </is>
       </c>
       <c r="F186" s="6" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="D187" s="8" t="inlineStr">
         <is>
-          <t>科目ごとに希望コマ数を＋／−する</t>
+          <t>すでに盤面に割り振られているコマを見る</t>
         </is>
       </c>
       <c r="E187" s="8" t="inlineStr">
         <is>
-          <t>数を入れられ、合計が表示される</t>
+          <t>青く表示され、そこには「講数」「通英」「振国」のように種別＋科目が出る</t>
         </is>
       </c>
       <c r="F187" s="6" t="inlineStr">
@@ -7664,9 +7664,9 @@
           <t>★★</t>
         </is>
       </c>
-      <c r="G187" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+      <c r="G187" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H187" s="6" t="n"/>
@@ -7688,12 +7688,12 @@
       </c>
       <c r="D188" s="8" t="inlineStr">
         <is>
-          <t>「通常授業のみ（講習なし）」にチェックする</t>
+          <t>すでに盤面にあるコマを不可にしようとする</t>
         </is>
       </c>
       <c r="E188" s="8" t="inlineStr">
         <is>
-          <t>講習ストックの対象外になる</t>
+          <t>確認が出る</t>
         </is>
       </c>
       <c r="F188" s="6" t="inlineStr">
@@ -7725,12 +7725,12 @@
       </c>
       <c r="D189" s="8" t="inlineStr">
         <is>
-          <t>希望科目の授業時間を選ぶ</t>
+          <t>休校日のマスを見る</t>
         </is>
       </c>
       <c r="E189" s="8" t="inlineStr">
         <is>
-          <t>科目ごとに90/60/45分を選べる（既定90）</t>
+          <t>灰色で選べない</t>
         </is>
       </c>
       <c r="F189" s="6" t="inlineStr">
@@ -7762,12 +7762,12 @@
       </c>
       <c r="D190" s="8" t="inlineStr">
         <is>
-          <t>「提出する」を押す</t>
+          <t>科目ごとに希望コマ数を＋／−する</t>
         </is>
       </c>
       <c r="E190" s="8" t="inlineStr">
         <is>
-          <t>確認のあと提出完了画面になり、本人からは変更できなくなる</t>
+          <t>数を入れられ、合計が表示される</t>
         </is>
       </c>
       <c r="F190" s="6" t="inlineStr">
@@ -7799,22 +7799,22 @@
       </c>
       <c r="D191" s="8" t="inlineStr">
         <is>
-          <t>提出済みのリンクをもう一度開く</t>
+          <t>「通常授業のみ（講習なし）」にチェックする</t>
         </is>
       </c>
       <c r="E191" s="8" t="inlineStr">
         <is>
-          <t>「すでに提出済みです」と出て、提出した内容が読み取り専用で確認できる</t>
+          <t>講習ストックの対象外になる</t>
         </is>
       </c>
       <c r="F191" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="G191" s="10" t="inlineStr">
-        <is>
-          <t>更新</t>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G191" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H191" s="6" t="n"/>
@@ -7836,12 +7836,12 @@
       </c>
       <c r="D192" s="8" t="inlineStr">
         <is>
-          <t>提出後の画面で希望コマ数（例「10コマ / 90分」）を見る</t>
+          <t>希望科目の授業時間を選ぶ</t>
         </is>
       </c>
       <c r="E192" s="8" t="inlineStr">
         <is>
-          <t>科目名と同じくらいの大きさで読める</t>
+          <t>科目ごとに90/60/45分を選べる（既定90）</t>
         </is>
       </c>
       <c r="F192" s="6" t="inlineStr">
@@ -7849,9 +7849,9 @@
           <t>★</t>
         </is>
       </c>
-      <c r="G192" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+      <c r="G192" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H192" s="6" t="n"/>
@@ -7873,12 +7873,12 @@
       </c>
       <c r="D193" s="8" t="inlineStr">
         <is>
-          <t>iPhone と Android の両方で不可コマの表を見る</t>
+          <t>「提出する」を押す</t>
         </is>
       </c>
       <c r="E193" s="8" t="inlineStr">
         <is>
-          <t>どちらも画面いっぱいの幅で表示される</t>
+          <t>確認のあと提出完了画面になり、本人からは変更できなくなる</t>
         </is>
       </c>
       <c r="F193" s="6" t="inlineStr">
@@ -7886,9 +7886,9 @@
           <t>★★</t>
         </is>
       </c>
-      <c r="G193" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+      <c r="G193" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H193" s="6" t="n"/>
@@ -7910,22 +7910,22 @@
       </c>
       <c r="D194" s="8" t="inlineStr">
         <is>
-          <t>無効なリンクを開く</t>
+          <t>提出済みのリンクをもう一度開く</t>
         </is>
       </c>
       <c r="E194" s="8" t="inlineStr">
         <is>
-          <t>「このリンクは無効です。管理者にお問い合わせください」と出る</t>
+          <t>「すでに提出済みです」と出て、提出した内容が読み取り専用で確認できる</t>
         </is>
       </c>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="G194" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G194" s="10" t="inlineStr">
+        <is>
+          <t>更新</t>
         </is>
       </c>
       <c r="H194" s="6" t="n"/>
@@ -7935,9 +7935,9 @@
       <c r="A195" s="6" t="n">
         <v>192</v>
       </c>
-      <c r="B195" s="7" t="inlineStr">
-        <is>
-          <t>17.QR提出（講師）</t>
+      <c r="B195" s="8" t="inlineStr">
+        <is>
+          <t>16.QR提出（保護者・生徒）</t>
         </is>
       </c>
       <c r="C195" s="6" t="inlineStr">
@@ -7947,22 +7947,22 @@
       </c>
       <c r="D195" s="8" t="inlineStr">
         <is>
-          <t>講師用QRリンクを開く</t>
+          <t>提出後の画面で希望コマ数（例「10コマ / 90分」）を見る</t>
         </is>
       </c>
       <c r="E195" s="8" t="inlineStr">
         <is>
-          <t>講師用の入力画面が表示される</t>
+          <t>科目名と同じくらいの大きさで読める</t>
         </is>
       </c>
       <c r="F195" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="G195" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G195" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H195" s="6" t="n"/>
@@ -7974,7 +7974,7 @@
       </c>
       <c r="B196" s="8" t="inlineStr">
         <is>
-          <t>17.QR提出（講師）</t>
+          <t>16.QR提出（保護者・生徒）</t>
         </is>
       </c>
       <c r="C196" s="6" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="D196" s="8" t="inlineStr">
         <is>
-          <t>出席不可コマを選んで提出する</t>
+          <t>iPhone と Android の両方で不可コマの表を見る</t>
         </is>
       </c>
       <c r="E196" s="8" t="inlineStr">
         <is>
-          <t>提出でき、以後は本人から変更できない</t>
+          <t>どちらも画面いっぱいの幅で表示される</t>
         </is>
       </c>
       <c r="F196" s="6" t="inlineStr">
@@ -7997,9 +7997,9 @@
           <t>★★</t>
         </is>
       </c>
-      <c r="G196" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+      <c r="G196" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H196" s="6" t="n"/>
@@ -8011,32 +8011,32 @@
       </c>
       <c r="B197" s="8" t="inlineStr">
         <is>
-          <t>17.QR提出（講師）</t>
+          <t>16.QR提出（保護者・生徒）</t>
         </is>
       </c>
       <c r="C197" s="6" t="inlineStr">
         <is>
-          <t>室長</t>
+          <t>提出</t>
         </is>
       </c>
       <c r="D197" s="8" t="inlineStr">
         <is>
-          <t>講師の提出後に盤面を見る</t>
+          <t>無効なリンクを開く</t>
         </is>
       </c>
       <c r="E197" s="8" t="inlineStr">
         <is>
-          <t>出席可能なコマの空いている机に、その講師の名前が自動で入る</t>
+          <t>「このリンクは無効です。管理者にお問い合わせください」と出る</t>
         </is>
       </c>
       <c r="F197" s="6" t="inlineStr">
         <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="G197" s="10" t="inlineStr">
-        <is>
-          <t>更新</t>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G197" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H197" s="6" t="n"/>
@@ -8046,34 +8046,34 @@
       <c r="A198" s="6" t="n">
         <v>195</v>
       </c>
-      <c r="B198" s="8" t="inlineStr">
+      <c r="B198" s="7" t="inlineStr">
         <is>
           <t>17.QR提出（講師）</t>
         </is>
       </c>
       <c r="C198" s="6" t="inlineStr">
         <is>
-          <t>室長</t>
+          <t>提出</t>
         </is>
       </c>
       <c r="D198" s="8" t="inlineStr">
         <is>
-          <t>複数の講師がまとめて提出した状態で教室を開く</t>
+          <t>講師用QRリンクを開く</t>
         </is>
       </c>
       <c r="E198" s="8" t="inlineStr">
         <is>
-          <t>全員ぶんが反映される（最後の1人だけにならない）</t>
+          <t>講師用の入力画面が表示される</t>
         </is>
       </c>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="G198" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G198" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H198" s="6" t="n"/>
@@ -8090,17 +8090,17 @@
       </c>
       <c r="C199" s="6" t="inlineStr">
         <is>
-          <t>室長</t>
+          <t>提出</t>
         </is>
       </c>
       <c r="D199" s="8" t="inlineStr">
         <is>
-          <t>講師の提出が反映された直後、手動保存せずに再読み込みする</t>
+          <t>出席不可コマを選んで提出する</t>
         </is>
       </c>
       <c r="E199" s="8" t="inlineStr">
         <is>
-          <t>起動時に自己修復され、講師の配置が復活する（消えたままにならない）</t>
+          <t>提出でき、以後は本人から変更できない</t>
         </is>
       </c>
       <c r="F199" s="6" t="inlineStr">
@@ -8108,9 +8108,9 @@
           <t>★★</t>
         </is>
       </c>
-      <c r="G199" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+      <c r="G199" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H199" s="6" t="n"/>
@@ -8120,9 +8120,9 @@
       <c r="A200" s="6" t="n">
         <v>197</v>
       </c>
-      <c r="B200" s="7" t="inlineStr">
-        <is>
-          <t>18.出席不可コマ・黄色コマ</t>
+      <c r="B200" s="8" t="inlineStr">
+        <is>
+          <t>17.QR提出（講師）</t>
         </is>
       </c>
       <c r="C200" s="6" t="inlineStr">
@@ -8132,22 +8132,22 @@
       </c>
       <c r="D200" s="8" t="inlineStr">
         <is>
-          <t>提出で「出席不可」になっているコマへ生徒を配置／移動／入替／手動追加する</t>
+          <t>講師の提出後に盤面を見る</t>
         </is>
       </c>
       <c r="E200" s="8" t="inlineStr">
         <is>
-          <t>確認ダイアログが出る（勝手には置かれない）</t>
+          <t>出席可能なコマの空いている机に、その講師の名前が自動で入る</t>
         </is>
       </c>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="G200" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="G200" s="10" t="inlineStr">
+        <is>
+          <t>更新</t>
         </is>
       </c>
       <c r="H200" s="6" t="n"/>
@@ -8159,7 +8159,7 @@
       </c>
       <c r="B201" s="8" t="inlineStr">
         <is>
-          <t>18.出席不可コマ・黄色コマ</t>
+          <t>17.QR提出（講師）</t>
         </is>
       </c>
       <c r="C201" s="6" t="inlineStr">
@@ -8169,12 +8169,12 @@
       </c>
       <c r="D201" s="8" t="inlineStr">
         <is>
-          <t>その確認ダイアログで承認する</t>
+          <t>複数の講師がまとめて提出した状態で教室を開く</t>
         </is>
       </c>
       <c r="E201" s="8" t="inlineStr">
         <is>
-          <t>そのコマが黄色になり、以後は普通の出席可能なコマとして扱われる</t>
+          <t>全員ぶんが反映される（最後の1人だけにならない）</t>
         </is>
       </c>
       <c r="F201" s="6" t="inlineStr">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="B202" s="8" t="inlineStr">
         <is>
-          <t>18.出席不可コマ・黄色コマ</t>
+          <t>17.QR提出（講師）</t>
         </is>
       </c>
       <c r="C202" s="6" t="inlineStr">
@@ -8206,12 +8206,12 @@
       </c>
       <c r="D202" s="8" t="inlineStr">
         <is>
-          <t>黄色になったコマの警告と自動割振を見る</t>
+          <t>講師の提出が反映された直後、手動保存せずに再読み込みする</t>
         </is>
       </c>
       <c r="E202" s="8" t="inlineStr">
         <is>
-          <t>赤い警告が消え、自動割振・自動配置の候補にもなる</t>
+          <t>起動時に自己修復され、講師の配置が復活する（消えたままにならない）</t>
         </is>
       </c>
       <c r="F202" s="6" t="inlineStr">
@@ -8231,7 +8231,7 @@
       <c r="A203" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="B203" s="8" t="inlineStr">
+      <c r="B203" s="7" t="inlineStr">
         <is>
           <t>18.出席不可コマ・黄色コマ</t>
         </is>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="D203" s="8" t="inlineStr">
         <is>
-          <t>講師日程表で不可セルをクリックする</t>
+          <t>提出で「出席不可」になっているコマへ生徒を配置／移動／入替／手動追加する</t>
         </is>
       </c>
       <c r="E203" s="8" t="inlineStr">
         <is>
-          <t>確認のあと黄色になる（講師側の黄色化）</t>
+          <t>確認ダイアログが出る（勝手には置かれない）</t>
         </is>
       </c>
       <c r="F203" s="6" t="inlineStr">
@@ -8280,17 +8280,17 @@
       </c>
       <c r="D204" s="8" t="inlineStr">
         <is>
-          <t>黄色にしたコマを日程表（画面・印刷）と保護者/講師のQR画面で見る</t>
+          <t>その確認ダイアログで承認する</t>
         </is>
       </c>
       <c r="E204" s="8" t="inlineStr">
         <is>
-          <t>どれも黄色＋注記で「後から出席可能になった」と分かる</t>
+          <t>そのコマが黄色になり、以後は普通の出席可能なコマとして扱われる</t>
         </is>
       </c>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★★★</t>
         </is>
       </c>
       <c r="G204" s="9" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="D205" s="8" t="inlineStr">
         <is>
-          <t>黄色にしたあと、その生徒/講師の登録を解除する</t>
+          <t>黄色になったコマの警告と自動割振を見る</t>
         </is>
       </c>
       <c r="E205" s="8" t="inlineStr">
         <is>
-          <t>黄色は保持される</t>
+          <t>赤い警告が消え、自動割振・自動配置の候補にもなる</t>
         </is>
       </c>
       <c r="F205" s="6" t="inlineStr">
@@ -8349,17 +8349,17 @@
       </c>
       <c r="C206" s="6" t="inlineStr">
         <is>
-          <t>提出</t>
+          <t>室長</t>
         </is>
       </c>
       <c r="D206" s="8" t="inlineStr">
         <is>
-          <t>黄色がある状態で、本人がQRから新しく提出し直す</t>
+          <t>講師日程表で不可セルをクリックする</t>
         </is>
       </c>
       <c r="E206" s="8" t="inlineStr">
         <is>
-          <t>黄色はリセットされ、新しい提出内容が正になる</t>
+          <t>確認のあと黄色になる（講師側の黄色化）</t>
         </is>
       </c>
       <c r="F206" s="6" t="inlineStr">
@@ -8391,17 +8391,17 @@
       </c>
       <c r="D207" s="8" t="inlineStr">
         <is>
-          <t>黄色を元（不可）に戻す操作を探す</t>
+          <t>黄色にしたコマを日程表（画面・印刷）と保護者/講師のQR画面で見る</t>
         </is>
       </c>
       <c r="E207" s="8" t="inlineStr">
         <is>
-          <t>戻す操作は無い（一方通行）</t>
+          <t>どれも黄色＋注記で「後から出席可能になった」と分かる</t>
         </is>
       </c>
       <c r="F207" s="6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="G207" s="9" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="D208" s="8" t="inlineStr">
         <is>
-          <t>以前から不可コマの上に置かれていた既存の配置を見る</t>
+          <t>黄色にしたあと、その生徒/講師の登録を解除する</t>
         </is>
       </c>
       <c r="E208" s="8" t="inlineStr">
         <is>
-          <t>自動では黄色に変換されない（新しい操作のときだけ）</t>
+          <t>黄色は保持される</t>
         </is>
       </c>
       <c r="F208" s="6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="G208" s="9" t="inlineStr">
@@ -8453,29 +8453,29 @@
       <c r="A209" s="6" t="n">
         <v>206</v>
       </c>
-      <c r="B209" s="7" t="inlineStr">
-        <is>
-          <t>19.提出の反映・通知</t>
+      <c r="B209" s="8" t="inlineStr">
+        <is>
+          <t>18.出席不可コマ・黄色コマ</t>
         </is>
       </c>
       <c r="C209" s="6" t="inlineStr">
         <is>
-          <t>室長</t>
+          <t>提出</t>
         </is>
       </c>
       <c r="D209" s="8" t="inlineStr">
         <is>
-          <t>PCを閉じている間にQR提出を1件入れておき、次にコマ表を開く</t>
+          <t>黄色がある状態で、本人がQRから新しく提出し直す</t>
         </is>
       </c>
       <c r="E209" s="8" t="inlineStr">
         <is>
-          <t>開いた最初にモーダルで「提出が届いた」と知らせる</t>
+          <t>黄色はリセットされ、新しい提出内容が正になる</t>
         </is>
       </c>
       <c r="F209" s="6" t="inlineStr">
         <is>
-          <t>★★★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="G209" s="9" t="inlineStr">
@@ -8492,7 +8492,7 @@
       </c>
       <c r="B210" s="8" t="inlineStr">
         <is>
-          <t>19.提出の反映・通知</t>
+          <t>18.出席不可コマ・黄色コマ</t>
         </is>
       </c>
       <c r="C210" s="6" t="inlineStr">
@@ -8502,17 +8502,17 @@
       </c>
       <c r="D210" s="8" t="inlineStr">
         <is>
-          <t>その通知を閉じたあと、ページを再読み込みする</t>
+          <t>黄色を元（不可）に戻す操作を探す</t>
         </is>
       </c>
       <c r="E210" s="8" t="inlineStr">
         <is>
-          <t>同じ提出でもう一度通知されない</t>
+          <t>戻す操作は無い（一方通行）</t>
         </is>
       </c>
       <c r="F210" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★</t>
         </is>
       </c>
       <c r="G210" s="9" t="inlineStr">
@@ -8529,7 +8529,7 @@
       </c>
       <c r="B211" s="8" t="inlineStr">
         <is>
-          <t>19.提出の反映・通知</t>
+          <t>18.出席不可コマ・黄色コマ</t>
         </is>
       </c>
       <c r="C211" s="6" t="inlineStr">
@@ -8539,22 +8539,22 @@
       </c>
       <c r="D211" s="8" t="inlineStr">
         <is>
-          <t>アプリを開いたまま、別端末からQR提出する</t>
+          <t>以前から不可コマの上に置かれていた既存の配置を見る</t>
         </is>
       </c>
       <c r="E211" s="8" t="inlineStr">
         <is>
-          <t>その場でモーダル通知が出て、盤面・出席者一覧にも反映される</t>
+          <t>自動では黄色に変換されない（新しい操作のときだけ）</t>
         </is>
       </c>
       <c r="F211" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="G211" s="10" t="inlineStr">
-        <is>
-          <t>更新</t>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G211" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H211" s="6" t="n"/>
@@ -8564,7 +8564,7 @@
       <c r="A212" s="6" t="n">
         <v>209</v>
       </c>
-      <c r="B212" s="8" t="inlineStr">
+      <c r="B212" s="7" t="inlineStr">
         <is>
           <t>19.提出の反映・通知</t>
         </is>
@@ -8576,17 +8576,17 @@
       </c>
       <c r="D212" s="8" t="inlineStr">
         <is>
-          <t>室長が日程表から自分で登録する</t>
+          <t>PCを閉じている間にQR提出を1件入れておき、次にコマ表を開く</t>
         </is>
       </c>
       <c r="E212" s="8" t="inlineStr">
         <is>
-          <t>自分の操作では提出モーダルは出ない</t>
+          <t>開いた最初にモーダルで「提出が届いた」と知らせる</t>
         </is>
       </c>
       <c r="F212" s="6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★★</t>
         </is>
       </c>
       <c r="G212" s="9" t="inlineStr">
@@ -8613,12 +8613,12 @@
       </c>
       <c r="D213" s="8" t="inlineStr">
         <is>
-          <t>提出者の登録を削除する（登録解除）</t>
+          <t>その通知を閉じたあと、ページを再読み込みする</t>
         </is>
       </c>
       <c r="E213" s="8" t="inlineStr">
         <is>
-          <t>提出がリセットされ、同じQRで再提出できるようになる</t>
+          <t>同じ提出でもう一度通知されない</t>
         </is>
       </c>
       <c r="F213" s="6" t="inlineStr">
@@ -8626,9 +8626,9 @@
           <t>★★</t>
         </is>
       </c>
-      <c r="G213" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+      <c r="G213" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H213" s="6" t="n"/>
@@ -8650,22 +8650,22 @@
       </c>
       <c r="D214" s="8" t="inlineStr">
         <is>
-          <t>登録解除した直後、しばらく画面を見ている／再読み込みする</t>
+          <t>アプリを開いたまま、別端末からQR提出する</t>
         </is>
       </c>
       <c r="E214" s="8" t="inlineStr">
         <is>
-          <t>解除した提出が勝手に復活しない（生徒・講師のどちらでも）</t>
+          <t>その場でモーダル通知が出て、盤面・出席者一覧にも反映される</t>
         </is>
       </c>
       <c r="F214" s="6" t="inlineStr">
         <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="G214" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G214" s="10" t="inlineStr">
+        <is>
+          <t>更新</t>
         </is>
       </c>
       <c r="H214" s="6" t="n"/>
@@ -8687,12 +8687,12 @@
       </c>
       <c r="D215" s="8" t="inlineStr">
         <is>
-          <t>登録を確定したあと本人が再提出を試す</t>
+          <t>室長が日程表から自分で登録する</t>
         </is>
       </c>
       <c r="E215" s="8" t="inlineStr">
         <is>
-          <t>確定後は再提出できない</t>
+          <t>自分の操作では提出モーダルは出ない</t>
         </is>
       </c>
       <c r="F215" s="6" t="inlineStr">
@@ -8700,9 +8700,9 @@
           <t>★</t>
         </is>
       </c>
-      <c r="G215" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+      <c r="G215" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H215" s="6" t="n"/>
@@ -8712,9 +8712,9 @@
       <c r="A216" s="6" t="n">
         <v>213</v>
       </c>
-      <c r="B216" s="7" t="inlineStr">
-        <is>
-          <t>20.集団授業</t>
+      <c r="B216" s="8" t="inlineStr">
+        <is>
+          <t>19.提出の反映・通知</t>
         </is>
       </c>
       <c r="C216" s="6" t="inlineStr">
@@ -8724,22 +8724,22 @@
       </c>
       <c r="D216" s="8" t="inlineStr">
         <is>
-          <t>盤面の集団行の空セルをクリックする</t>
+          <t>提出者の登録を削除する（登録解除）</t>
         </is>
       </c>
       <c r="E216" s="8" t="inlineStr">
         <is>
-          <t>科目ピッカー（集団理科／集団社会）が出る</t>
+          <t>提出がリセットされ、同じQRで再提出できるようになる</t>
         </is>
       </c>
       <c r="F216" s="6" t="inlineStr">
         <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="G216" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G216" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H216" s="6" t="n"/>
@@ -8751,7 +8751,7 @@
       </c>
       <c r="B217" s="8" t="inlineStr">
         <is>
-          <t>20.集団授業</t>
+          <t>19.提出の反映・通知</t>
         </is>
       </c>
       <c r="C217" s="6" t="inlineStr">
@@ -8761,17 +8761,17 @@
       </c>
       <c r="D217" s="8" t="inlineStr">
         <is>
-          <t>科目が入った集団セルをクリックする</t>
+          <t>登録解除した直後、しばらく画面を見ている／再読み込みする</t>
         </is>
       </c>
       <c r="E217" s="8" t="inlineStr">
         <is>
-          <t>「出席者一覧／削除」のメニューが出る</t>
+          <t>解除した提出が勝手に復活しない（生徒・講師のどちらでも）</t>
         </is>
       </c>
       <c r="F217" s="6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★★</t>
         </is>
       </c>
       <c r="G217" s="9" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="B218" s="8" t="inlineStr">
         <is>
-          <t>20.集団授業</t>
+          <t>19.提出の反映・通知</t>
         </is>
       </c>
       <c r="C218" s="6" t="inlineStr">
@@ -8798,22 +8798,22 @@
       </c>
       <c r="D218" s="8" t="inlineStr">
         <is>
-          <t>「出席者一覧」で生徒を選んで保存する</t>
+          <t>登録を確定したあと本人が再提出を試す</t>
         </is>
       </c>
       <c r="E218" s="8" t="inlineStr">
         <is>
-          <t>出席状況が保存され、再度開いても残っている</t>
+          <t>確定後は再提出できない</t>
         </is>
       </c>
       <c r="F218" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="G218" s="10" t="inlineStr">
-        <is>
-          <t>更新</t>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G218" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H218" s="6" t="n"/>
@@ -8823,7 +8823,7 @@
       <c r="A219" s="6" t="n">
         <v>216</v>
       </c>
-      <c r="B219" s="8" t="inlineStr">
+      <c r="B219" s="7" t="inlineStr">
         <is>
           <t>20.集団授業</t>
         </is>
@@ -8835,12 +8835,12 @@
       </c>
       <c r="D219" s="8" t="inlineStr">
         <is>
-          <t>出席者一覧を「PDF印刷」する</t>
+          <t>盤面の集団行の空セルをクリックする</t>
         </is>
       </c>
       <c r="E219" s="8" t="inlineStr">
         <is>
-          <t>内容の幅で左詰めに出て、手書き用の「チェック欄」列がある</t>
+          <t>科目ピッカー（集団理科／集団社会）が出る</t>
         </is>
       </c>
       <c r="F219" s="6" t="inlineStr">
@@ -8872,17 +8872,17 @@
       </c>
       <c r="D220" s="8" t="inlineStr">
         <is>
-          <t>その講習期間に集団科目を1度も盤面に置いていない状態で、日程表の登録画面とQR提出画面を見る</t>
+          <t>科目が入った集団セルをクリックする</t>
         </is>
       </c>
       <c r="E220" s="8" t="inlineStr">
         <is>
-          <t>集団授業の欄が出ない（中3でも出ない）</t>
+          <t>「出席者一覧／削除」のメニューが出る</t>
         </is>
       </c>
       <c r="F220" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★</t>
         </is>
       </c>
       <c r="G220" s="9" t="inlineStr">
@@ -8909,12 +8909,12 @@
       </c>
       <c r="D221" s="8" t="inlineStr">
         <is>
-          <t>生徒日程表の登録から集団参加を保存する</t>
+          <t>「出席者一覧」で生徒を選んで保存する</t>
         </is>
       </c>
       <c r="E221" s="8" t="inlineStr">
         <is>
-          <t>出席者一覧に反映される</t>
+          <t>出席状況が保存され、再度開いても残っている</t>
         </is>
       </c>
       <c r="F221" s="6" t="inlineStr">
@@ -8922,9 +8922,9 @@
           <t>★★</t>
         </is>
       </c>
-      <c r="G221" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+      <c r="G221" s="10" t="inlineStr">
+        <is>
+          <t>更新</t>
         </is>
       </c>
       <c r="H221" s="6" t="n"/>
@@ -8934,9 +8934,9 @@
       <c r="A222" s="6" t="n">
         <v>219</v>
       </c>
-      <c r="B222" s="7" t="inlineStr">
-        <is>
-          <t>21.自動割振ルール</t>
+      <c r="B222" s="8" t="inlineStr">
+        <is>
+          <t>20.集団授業</t>
         </is>
       </c>
       <c r="C222" s="6" t="inlineStr">
@@ -8946,22 +8946,22 @@
       </c>
       <c r="D222" s="8" t="inlineStr">
         <is>
-          <t>ルール画面で区分を設定する</t>
+          <t>出席者一覧を「PDF印刷」する</t>
         </is>
       </c>
       <c r="E222" s="8" t="inlineStr">
         <is>
-          <t>各ルールを優先事項／制約事項に設定できる</t>
+          <t>内容の幅で左詰めに出て、手書き用の「チェック欄」列がある</t>
         </is>
       </c>
       <c r="F222" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="G222" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G222" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H222" s="6" t="n"/>
@@ -8973,7 +8973,7 @@
       </c>
       <c r="B223" s="8" t="inlineStr">
         <is>
-          <t>21.自動割振ルール</t>
+          <t>20.集団授業</t>
         </is>
       </c>
       <c r="C223" s="6" t="inlineStr">
@@ -8983,22 +8983,22 @@
       </c>
       <c r="D223" s="8" t="inlineStr">
         <is>
-          <t>絶対事項のルールを変えようとする</t>
+          <t>その講習期間に集団科目を1度も盤面に置いていない状態で、日程表の登録画面とQR提出画面を見る</t>
         </is>
       </c>
       <c r="E223" s="8" t="inlineStr">
         <is>
-          <t>絶対事項は編集できず、他ルールを絶対事項にもできない</t>
+          <t>集団授業の欄が出ない（中3でも出ない）</t>
         </is>
       </c>
       <c r="F223" s="6" t="inlineStr">
         <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="G223" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G223" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H223" s="6" t="n"/>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="B224" s="8" t="inlineStr">
         <is>
-          <t>21.自動割振ルール</t>
+          <t>20.集団授業</t>
         </is>
       </c>
       <c r="C224" s="6" t="inlineStr">
@@ -9020,12 +9020,12 @@
       </c>
       <c r="D224" s="8" t="inlineStr">
         <is>
-          <t>画面冒頭の説明文を読む</t>
+          <t>生徒日程表の登録から集団参加を保存する</t>
         </is>
       </c>
       <c r="E224" s="8" t="inlineStr">
         <is>
-          <t>「制約事項を守れない候補は割り振らず未消化に残す」というハードな挙動の説明になっている</t>
+          <t>出席者一覧に反映される</t>
         </is>
       </c>
       <c r="F224" s="6" t="inlineStr">
@@ -9033,9 +9033,9 @@
           <t>★★</t>
         </is>
       </c>
-      <c r="G224" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+      <c r="G224" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H224" s="6" t="n"/>
@@ -9045,7 +9045,7 @@
       <c r="A225" s="6" t="n">
         <v>222</v>
       </c>
-      <c r="B225" s="8" t="inlineStr">
+      <c r="B225" s="7" t="inlineStr">
         <is>
           <t>21.自動割振ルール</t>
         </is>
@@ -9057,17 +9057,17 @@
       </c>
       <c r="D225" s="8" t="inlineStr">
         <is>
-          <t>登校日（集約／分散）ルールを設定する</t>
+          <t>ルール画面で区分を設定する</t>
         </is>
       </c>
       <c r="E225" s="8" t="inlineStr">
         <is>
-          <t>設定が効く</t>
+          <t>各ルールを優先事項／制約事項に設定できる</t>
         </is>
       </c>
       <c r="F225" s="6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="G225" s="6" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="D226" s="8" t="inlineStr">
         <is>
-          <t>「講師1人に生徒2人」ルールを設定する</t>
+          <t>絶対事項のルールを変えようとする</t>
         </is>
       </c>
       <c r="E226" s="8" t="inlineStr">
         <is>
-          <t>設定が効く</t>
+          <t>絶対事項は編集できず、他ルールを絶対事項にもできない</t>
         </is>
       </c>
       <c r="F226" s="6" t="inlineStr">
@@ -9131,22 +9131,22 @@
       </c>
       <c r="D227" s="8" t="inlineStr">
         <is>
-          <t>同日コマ数上限（1/2/3コマ）を設定する</t>
+          <t>画面冒頭の説明文を読む</t>
         </is>
       </c>
       <c r="E227" s="8" t="inlineStr">
         <is>
-          <t>上限が効く</t>
+          <t>「制約事項を守れない候補は割り振らず未消化に残す」というハードな挙動の説明になっている</t>
         </is>
       </c>
       <c r="F227" s="6" t="inlineStr">
         <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="G227" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G227" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H227" s="6" t="n"/>
@@ -9168,7 +9168,7 @@
       </c>
       <c r="D228" s="8" t="inlineStr">
         <is>
-          <t>連続・間隔（2コマ連続/一コマ空け/通常連結）を設定する</t>
+          <t>登校日（集約／分散）ルールを設定する</t>
         </is>
       </c>
       <c r="E228" s="8" t="inlineStr">
@@ -9205,17 +9205,17 @@
       </c>
       <c r="D229" s="8" t="inlineStr">
         <is>
-          <t>「科目対応講師のみ」を設定する</t>
+          <t>「講師1人に生徒2人」ルールを設定する</t>
         </is>
       </c>
       <c r="E229" s="8" t="inlineStr">
         <is>
-          <t>担当科目内の生徒だけに配置される</t>
+          <t>設定が効く</t>
         </is>
       </c>
       <c r="F229" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★</t>
         </is>
       </c>
       <c r="G229" s="6" t="inlineStr">
@@ -9242,17 +9242,17 @@
       </c>
       <c r="D230" s="8" t="inlineStr">
         <is>
-          <t>「通常講師のみ」を設定する</t>
+          <t>同日コマ数上限（1/2/3コマ）を設定する</t>
         </is>
       </c>
       <c r="E230" s="8" t="inlineStr">
         <is>
-          <t>通常授業の担当講師に制限される</t>
+          <t>上限が効く</t>
         </is>
       </c>
       <c r="F230" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★</t>
         </is>
       </c>
       <c r="G230" s="6" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="D231" s="8" t="inlineStr">
         <is>
-          <t>「科目分散」ルールを見る</t>
+          <t>連続・間隔（2コマ連続/一コマ空け/通常連結）を設定する</t>
         </is>
       </c>
       <c r="E231" s="8" t="inlineStr">
         <is>
-          <t>ルールとして存在し、既定は優先事項（制約事項には設定できない）</t>
+          <t>設定が効く</t>
         </is>
       </c>
       <c r="F231" s="6" t="inlineStr">
@@ -9292,9 +9292,9 @@
           <t>★</t>
         </is>
       </c>
-      <c r="G231" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+      <c r="G231" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H231" s="6" t="n"/>
@@ -9316,17 +9316,17 @@
       </c>
       <c r="D232" s="8" t="inlineStr">
         <is>
-          <t>時限優先スライダーで順序を変える</t>
+          <t>「科目対応講師のみ」を設定する</t>
         </is>
       </c>
       <c r="E232" s="8" t="inlineStr">
         <is>
-          <t>1〜5限の優先順を並べ替えでき、割振に反映される</t>
+          <t>担当科目内の生徒だけに配置される</t>
         </is>
       </c>
       <c r="F232" s="6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="G232" s="6" t="inlineStr">
@@ -9353,12 +9353,12 @@
       </c>
       <c r="D233" s="8" t="inlineStr">
         <is>
-          <t>指定時限禁止スライダーで時限を指定する</t>
+          <t>「通常講師のみ」を設定する</t>
         </is>
       </c>
       <c r="E233" s="8" t="inlineStr">
         <is>
-          <t>指定した時限が避けられる</t>
+          <t>通常授業の担当講師に制限される</t>
         </is>
       </c>
       <c r="F233" s="6" t="inlineStr">
@@ -9390,12 +9390,12 @@
       </c>
       <c r="D234" s="8" t="inlineStr">
         <is>
-          <t>ルールに＋対象／−対象（全員/学年/個別）を指定する</t>
+          <t>「科目分散」ルールを見る</t>
         </is>
       </c>
       <c r="E234" s="8" t="inlineStr">
         <is>
-          <t>対象・除外を指定でき、重なったら除外が優先される</t>
+          <t>ルールとして存在し、既定は優先事項（制約事項には設定できない）</t>
         </is>
       </c>
       <c r="F234" s="6" t="inlineStr">
@@ -9403,9 +9403,9 @@
           <t>★</t>
         </is>
       </c>
-      <c r="G234" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+      <c r="G234" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H234" s="6" t="n"/>
@@ -9427,12 +9427,12 @@
       </c>
       <c r="D235" s="8" t="inlineStr">
         <is>
-          <t>ルールグループの優先順位を上げ下げする</t>
+          <t>時限優先スライダーで順序を変える</t>
         </is>
       </c>
       <c r="E235" s="8" t="inlineStr">
         <is>
-          <t>順位を変えられる</t>
+          <t>1〜5限の優先順を並べ替えでき、割振に反映される</t>
         </is>
       </c>
       <c r="F235" s="6" t="inlineStr">
@@ -9464,12 +9464,12 @@
       </c>
       <c r="D236" s="8" t="inlineStr">
         <is>
-          <t>ペア制約「この2人は同席させない」を登録する</t>
+          <t>指定時限禁止スライダーで時限を指定する</t>
         </is>
       </c>
       <c r="E236" s="8" t="inlineStr">
         <is>
-          <t>登録でき、既定は制約事項（優先にも変更可）</t>
+          <t>指定した時限が避けられる</t>
         </is>
       </c>
       <c r="F236" s="6" t="inlineStr">
@@ -9501,12 +9501,12 @@
       </c>
       <c r="D237" s="8" t="inlineStr">
         <is>
-          <t>ルール・ペア制約をExcelで出力／取込する</t>
+          <t>ルールに＋対象／−対象（全員/学年/個別）を指定する</t>
         </is>
       </c>
       <c r="E237" s="8" t="inlineStr">
         <is>
-          <t>出力・取込ができる</t>
+          <t>対象・除外を指定でき、重なったら除外が優先される</t>
         </is>
       </c>
       <c r="F237" s="6" t="inlineStr">
@@ -9526,29 +9526,29 @@
       <c r="A238" s="6" t="n">
         <v>235</v>
       </c>
-      <c r="B238" s="7" t="inlineStr">
-        <is>
-          <t>22.自動割振の実行</t>
+      <c r="B238" s="8" t="inlineStr">
+        <is>
+          <t>21.自動割振ルール</t>
         </is>
       </c>
       <c r="C238" s="6" t="inlineStr">
         <is>
-          <t>共通</t>
+          <t>室長</t>
         </is>
       </c>
       <c r="D238" s="8" t="inlineStr">
         <is>
-          <t>「自動割振」を実行する</t>
+          <t>ルールグループの優先順位を上げ下げする</t>
         </is>
       </c>
       <c r="E238" s="8" t="inlineStr">
         <is>
-          <t>振替・講習が空きコマへ自動配置される</t>
+          <t>順位を変えられる</t>
         </is>
       </c>
       <c r="F238" s="6" t="inlineStr">
         <is>
-          <t>★★★</t>
+          <t>★</t>
         </is>
       </c>
       <c r="G238" s="6" t="inlineStr">
@@ -9565,32 +9565,32 @@
       </c>
       <c r="B239" s="8" t="inlineStr">
         <is>
-          <t>22.自動割振の実行</t>
+          <t>21.自動割振ルール</t>
         </is>
       </c>
       <c r="C239" s="6" t="inlineStr">
         <is>
-          <t>共通</t>
+          <t>室長</t>
         </is>
       </c>
       <c r="D239" s="8" t="inlineStr">
         <is>
-          <t>守れないと分かっている条件を「制約事項」にして自動割振する</t>
+          <t>ペア制約「この2人は同席させない」を登録する</t>
         </is>
       </c>
       <c r="E239" s="8" t="inlineStr">
         <is>
-          <t>違反する席には置かず、置けない分は未消化ストックに残る（無理に埋めない）</t>
+          <t>登録でき、既定は制約事項（優先にも変更可）</t>
         </is>
       </c>
       <c r="F239" s="6" t="inlineStr">
         <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="G239" s="10" t="inlineStr">
-        <is>
-          <t>更新</t>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G239" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H239" s="6" t="n"/>
@@ -9602,32 +9602,32 @@
       </c>
       <c r="B240" s="8" t="inlineStr">
         <is>
-          <t>22.自動割振の実行</t>
+          <t>21.自動割振ルール</t>
         </is>
       </c>
       <c r="C240" s="6" t="inlineStr">
         <is>
-          <t>共通</t>
+          <t>室長</t>
         </is>
       </c>
       <c r="D240" s="8" t="inlineStr">
         <is>
-          <t>同じ条件を「優先事項」に変えて自動割振する</t>
+          <t>ルール・ペア制約をExcelで出力／取込する</t>
         </is>
       </c>
       <c r="E240" s="8" t="inlineStr">
         <is>
-          <t>置ける場所が無ければ違反してでも配置され、警告で分かる</t>
+          <t>出力・取込ができる</t>
         </is>
       </c>
       <c r="F240" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="G240" s="10" t="inlineStr">
-        <is>
-          <t>更新</t>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G240" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H240" s="6" t="n"/>
@@ -9637,7 +9637,7 @@
       <c r="A241" s="6" t="n">
         <v>238</v>
       </c>
-      <c r="B241" s="8" t="inlineStr">
+      <c r="B241" s="7" t="inlineStr">
         <is>
           <t>22.自動割振の実行</t>
         </is>
@@ -9649,22 +9649,22 @@
       </c>
       <c r="D241" s="8" t="inlineStr">
         <is>
-          <t>割振の結果を見る</t>
+          <t>「自動割振」を実行する</t>
         </is>
       </c>
       <c r="E241" s="8" t="inlineStr">
         <is>
-          <t>制約違反の席が残っていない。避けた理由がメッセージで分かる</t>
+          <t>振替・講習が空きコマへ自動配置される</t>
         </is>
       </c>
       <c r="F241" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="G241" s="10" t="inlineStr">
-        <is>
-          <t>更新</t>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="G241" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H241" s="6" t="n"/>
@@ -9686,22 +9686,22 @@
       </c>
       <c r="D242" s="8" t="inlineStr">
         <is>
-          <t>通常授業（通）のコマを見る</t>
+          <t>守れないと分かっている条件を「制約事項」にして自動割振する</t>
         </is>
       </c>
       <c r="E242" s="8" t="inlineStr">
         <is>
-          <t>指定時限禁止・通常講師のみ・ペア制約などの警告対象にならない（誤警告が出ない）</t>
+          <t>違反する席には置かず、置けない分は未消化ストックに残る（無理に埋めない）</t>
         </is>
       </c>
       <c r="F242" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="G242" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="G242" s="10" t="inlineStr">
+        <is>
+          <t>更新</t>
         </is>
       </c>
       <c r="H242" s="6" t="n"/>
@@ -9723,12 +9723,12 @@
       </c>
       <c r="D243" s="8" t="inlineStr">
         <is>
-          <t>基本データで担当講師を編集した直後に「通常講師のみ」で割振する</t>
+          <t>同じ条件を「優先事項」に変えて自動割振する</t>
         </is>
       </c>
       <c r="E243" s="8" t="inlineStr">
         <is>
-          <t>盤面の通常授業の実態から判定され、許可講師がいきなり空にならない</t>
+          <t>置ける場所が無ければ違反してでも配置され、警告で分かる</t>
         </is>
       </c>
       <c r="F243" s="6" t="inlineStr">
@@ -9736,9 +9736,9 @@
           <t>★★</t>
         </is>
       </c>
-      <c r="G243" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+      <c r="G243" s="10" t="inlineStr">
+        <is>
+          <t>更新</t>
         </is>
       </c>
       <c r="H243" s="6" t="n"/>
@@ -9760,12 +9760,12 @@
       </c>
       <c r="D244" s="8" t="inlineStr">
         <is>
-          <t>振替と講習が両方残っている状態で自動割振する</t>
+          <t>割振の結果を見る</t>
         </is>
       </c>
       <c r="E244" s="8" t="inlineStr">
         <is>
-          <t>振替も講習と同時に割り当てられる</t>
+          <t>制約違反の席が残っていない。避けた理由がメッセージで分かる</t>
         </is>
       </c>
       <c r="F244" s="6" t="inlineStr">
@@ -9773,9 +9773,9 @@
           <t>★★</t>
         </is>
       </c>
-      <c r="G244" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+      <c r="G244" s="10" t="inlineStr">
+        <is>
+          <t>更新</t>
         </is>
       </c>
       <c r="H244" s="6" t="n"/>
@@ -9797,17 +9797,17 @@
       </c>
       <c r="D245" s="8" t="inlineStr">
         <is>
-          <t>割り振れなかった生徒がいる場合のメッセージを見る</t>
+          <t>通常授業（通）のコマを見る</t>
         </is>
       </c>
       <c r="E245" s="8" t="inlineStr">
         <is>
-          <t>誰がなぜ割り振れなかったかが分かる</t>
+          <t>指定時限禁止・通常講師のみ・ペア制約などの警告対象にならない（誤警告が出ない）</t>
         </is>
       </c>
       <c r="F245" s="6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="G245" s="9" t="inlineStr">
@@ -9822,24 +9822,24 @@
       <c r="A246" s="6" t="n">
         <v>243</v>
       </c>
-      <c r="B246" s="7" t="inlineStr">
-        <is>
-          <t>23.生徒日程表</t>
+      <c r="B246" s="8" t="inlineStr">
+        <is>
+          <t>22.自動割振の実行</t>
         </is>
       </c>
       <c r="C246" s="6" t="inlineStr">
         <is>
-          <t>室長</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="D246" s="8" t="inlineStr">
         <is>
-          <t>生徒の日程表を開く</t>
+          <t>基本データで担当講師を編集した直後に「通常講師のみ」で割振する</t>
         </is>
       </c>
       <c r="E246" s="8" t="inlineStr">
         <is>
-          <t>別タブでHTML表示され、タブ名が教室名になっている</t>
+          <t>盤面の通常授業の実態から判定され、許可講師がいきなり空にならない</t>
         </is>
       </c>
       <c r="F246" s="6" t="inlineStr">
@@ -9847,9 +9847,9 @@
           <t>★★</t>
         </is>
       </c>
-      <c r="G246" s="10" t="inlineStr">
-        <is>
-          <t>更新</t>
+      <c r="G246" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H246" s="6" t="n"/>
@@ -9861,27 +9861,27 @@
       </c>
       <c r="B247" s="8" t="inlineStr">
         <is>
-          <t>23.生徒日程表</t>
+          <t>22.自動割振の実行</t>
         </is>
       </c>
       <c r="C247" s="6" t="inlineStr">
         <is>
-          <t>室長</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="D247" s="8" t="inlineStr">
         <is>
-          <t>校舎名・ロゴと期間入力を見る</t>
+          <t>振替と講習が両方残っている状態で自動割振する</t>
         </is>
       </c>
       <c r="E247" s="8" t="inlineStr">
         <is>
-          <t>校舎名・ロゴは共通、期間は生徒/講師で別に保てる</t>
+          <t>振替も講習と同時に割り当てられる</t>
         </is>
       </c>
       <c r="F247" s="6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="G247" s="6" t="inlineStr">
@@ -9898,32 +9898,32 @@
       </c>
       <c r="B248" s="8" t="inlineStr">
         <is>
-          <t>23.生徒日程表</t>
+          <t>22.自動割振の実行</t>
         </is>
       </c>
       <c r="C248" s="6" t="inlineStr">
         <is>
-          <t>室長</t>
+          <t>共通</t>
         </is>
       </c>
       <c r="D248" s="8" t="inlineStr">
         <is>
-          <t>期間や生徒を変えて「最新表示」を押す</t>
+          <t>割り振れなかった生徒がいる場合のメッセージを見る</t>
         </is>
       </c>
       <c r="E248" s="8" t="inlineStr">
         <is>
-          <t>押したときに反映される</t>
+          <t>誰がなぜ割り振れなかったかが分かる</t>
         </is>
       </c>
       <c r="F248" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="G248" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G248" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H248" s="6" t="n"/>
@@ -9933,7 +9933,7 @@
       <c r="A249" s="6" t="n">
         <v>246</v>
       </c>
-      <c r="B249" s="8" t="inlineStr">
+      <c r="B249" s="7" t="inlineStr">
         <is>
           <t>23.生徒日程表</t>
         </is>
@@ -9945,22 +9945,22 @@
       </c>
       <c r="D249" s="8" t="inlineStr">
         <is>
-          <t>日程表タブを開いたまま、コマ表で席を動かす</t>
+          <t>生徒の日程表を開く</t>
         </is>
       </c>
       <c r="E249" s="8" t="inlineStr">
         <is>
-          <t>数秒で日程表タブに自動反映され、その間「コマ表の最新を反映中…」のスピナーが出る</t>
+          <t>別タブでHTML表示され、タブ名が教室名になっている</t>
         </is>
       </c>
       <c r="F249" s="6" t="inlineStr">
         <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="G249" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G249" s="10" t="inlineStr">
+        <is>
+          <t>更新</t>
         </is>
       </c>
       <c r="H249" s="6" t="n"/>
@@ -9982,17 +9982,17 @@
       </c>
       <c r="D250" s="8" t="inlineStr">
         <is>
-          <t>日程表のセルの中身を見る</t>
+          <t>校舎名・ロゴと期間入力を見る</t>
         </is>
       </c>
       <c r="E250" s="8" t="inlineStr">
         <is>
-          <t>盤面の実際だけが出る（予定だけのコマは出ない）</t>
+          <t>校舎名・ロゴは共通、期間は生徒/講師で別に保てる</t>
         </is>
       </c>
       <c r="F250" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★</t>
         </is>
       </c>
       <c r="G250" s="6" t="inlineStr">
@@ -10019,17 +10019,17 @@
       </c>
       <c r="D251" s="8" t="inlineStr">
         <is>
-          <t>未割当の振替ストックを日程表で探す</t>
+          <t>期間や生徒を変えて「最新表示」を押す</t>
         </is>
       </c>
       <c r="E251" s="8" t="inlineStr">
         <is>
-          <t>出てこない（実際に置いた振替だけ出る）</t>
+          <t>押したときに反映される</t>
         </is>
       </c>
       <c r="F251" s="6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="G251" s="6" t="inlineStr">
@@ -10056,22 +10056,22 @@
       </c>
       <c r="D252" s="8" t="inlineStr">
         <is>
-          <t>振替・講習の表示ラベルを見る</t>
+          <t>日程表タブを開いたまま、コマ表で席を動かす</t>
         </is>
       </c>
       <c r="E252" s="8" t="inlineStr">
         <is>
-          <t>『振)』『講)』と表示され、元コマに戻すと通常に戻る</t>
+          <t>数秒で日程表タブに自動反映され、その間「コマ表の最新を反映中…」のスピナーが出る</t>
         </is>
       </c>
       <c r="F252" s="6" t="inlineStr">
         <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="G252" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="G252" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H252" s="6" t="n"/>
@@ -10093,17 +10093,17 @@
       </c>
       <c r="D253" s="8" t="inlineStr">
         <is>
-          <t>講習の授業時間表示を見る</t>
+          <t>日程表のセルの中身を見る</t>
         </is>
       </c>
       <c r="E253" s="8" t="inlineStr">
         <is>
-          <t>90/60/45が反映される（例：講)小5算60）</t>
+          <t>盤面の実際だけが出る（予定だけのコマは出ない）</t>
         </is>
       </c>
       <c r="F253" s="6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="G253" s="6" t="inlineStr">
@@ -10130,12 +10130,12 @@
       </c>
       <c r="D254" s="8" t="inlineStr">
         <is>
-          <t>まだ盤面に置いていない希望科目の授業時間表示を見る</t>
+          <t>未割当の振替ストックを日程表で探す</t>
         </is>
       </c>
       <c r="E254" s="8" t="inlineStr">
         <is>
-          <t>希望登録の60/45分が表示される（分数が消えない）</t>
+          <t>出てこない（実際に置いた振替だけ出る）</t>
         </is>
       </c>
       <c r="F254" s="6" t="inlineStr">
@@ -10143,9 +10143,9 @@
           <t>★</t>
         </is>
       </c>
-      <c r="G254" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+      <c r="G254" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H254" s="6" t="n"/>
@@ -10167,17 +10167,17 @@
       </c>
       <c r="D255" s="8" t="inlineStr">
         <is>
-          <t>通常回数の表を見る</t>
+          <t>振替・講習の表示ラベルを見る</t>
         </is>
       </c>
       <c r="E255" s="8" t="inlineStr">
         <is>
-          <t>左＝実際／右かっこ＝予定。ズレると下に注意マークが出る</t>
+          <t>『振)』『講)』と表示され、元コマに戻すと通常に戻る</t>
         </is>
       </c>
       <c r="F255" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★</t>
         </is>
       </c>
       <c r="G255" s="6" t="inlineStr">
@@ -10204,12 +10204,12 @@
       </c>
       <c r="D256" s="8" t="inlineStr">
         <is>
-          <t>講習回数の表を見る</t>
+          <t>講習の授業時間表示を見る</t>
         </is>
       </c>
       <c r="E256" s="8" t="inlineStr">
         <is>
-          <t>左＝配置済み／右かっこ＝希望数。ズレると下に注意マークが出る</t>
+          <t>90/60/45が反映される（例：講)小5算60）</t>
         </is>
       </c>
       <c r="F256" s="6" t="inlineStr">
@@ -10241,17 +10241,17 @@
       </c>
       <c r="D257" s="8" t="inlineStr">
         <is>
-          <t>盤面に置いた通常授業が回数表に数えられているか見る</t>
+          <t>まだ盤面に置いていない希望科目の授業時間表示を見る</t>
         </is>
       </c>
       <c r="E257" s="8" t="inlineStr">
         <is>
-          <t>実際に置いた通常授業がきちんとカウントされる</t>
+          <t>希望登録の60/45分が表示される（分数が消えない）</t>
         </is>
       </c>
       <c r="F257" s="6" t="inlineStr">
         <is>
-          <t>★★★</t>
+          <t>★</t>
         </is>
       </c>
       <c r="G257" s="9" t="inlineStr">
@@ -10278,17 +10278,17 @@
       </c>
       <c r="D258" s="8" t="inlineStr">
         <is>
-          <t>小学生と中学生以上の科目表示を見る</t>
+          <t>通常回数の表を見る</t>
         </is>
       </c>
       <c r="E258" s="8" t="inlineStr">
         <is>
-          <t>算と数を同時に出さない（小=算／中以上=数）</t>
+          <t>左＝実際／右かっこ＝予定。ズレると下に注意マークが出る</t>
         </is>
       </c>
       <c r="F258" s="6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="G258" s="6" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="D259" s="8" t="inlineStr">
         <is>
-          <t>理社の生徒の回数表を見る</t>
+          <t>講習回数の表を見る</t>
         </is>
       </c>
       <c r="E259" s="8" t="inlineStr">
         <is>
-          <t>「社」の直後に1行だけ出る（理と社で2行に増えない）</t>
+          <t>左＝配置済み／右かっこ＝希望数。ズレると下に注意マークが出る</t>
         </is>
       </c>
       <c r="F259" s="6" t="inlineStr">
@@ -10328,9 +10328,9 @@
           <t>★</t>
         </is>
       </c>
-      <c r="G259" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+      <c r="G259" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H259" s="6" t="n"/>
@@ -10352,22 +10352,22 @@
       </c>
       <c r="D260" s="8" t="inlineStr">
         <is>
-          <t>日程表の色分けを見る</t>
+          <t>盤面に置いた通常授業が回数表に数えられているか見る</t>
         </is>
       </c>
       <c r="E260" s="8" t="inlineStr">
         <is>
-          <t>色分けは無く、通)/振)/講)のラベルで区別（注意の赤字は残る）</t>
+          <t>実際に置いた通常授業がきちんとカウントされる</t>
         </is>
       </c>
       <c r="F260" s="6" t="inlineStr">
         <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="G260" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="G260" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H260" s="6" t="n"/>
@@ -10389,12 +10389,12 @@
       </c>
       <c r="D261" s="8" t="inlineStr">
         <is>
-          <t>日程表のQR表示を見る</t>
+          <t>小学生と中学生以上の科目表示を見る</t>
         </is>
       </c>
       <c r="E261" s="8" t="inlineStr">
         <is>
-          <t>どの教室でも表示される</t>
+          <t>算と数を同時に出さない（小=算／中以上=数）</t>
         </is>
       </c>
       <c r="F261" s="6" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="D262" s="8" t="inlineStr">
         <is>
-          <t>日程表の下段の欄を見る</t>
+          <t>理社の生徒の回数表を見る</t>
         </is>
       </c>
       <c r="E262" s="8" t="inlineStr">
         <is>
-          <t>休み欄が無く、振替授業欄が左に寄り、右にオプション欄（2列×5行）がある</t>
+          <t>「社」の直後に1行だけ出る（理と社で2行に増えない）</t>
         </is>
       </c>
       <c r="F262" s="6" t="inlineStr">
@@ -10439,9 +10439,9 @@
           <t>★</t>
         </is>
       </c>
-      <c r="G262" s="10" t="inlineStr">
-        <is>
-          <t>更新</t>
+      <c r="G262" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H262" s="6" t="n"/>
@@ -10463,22 +10463,22 @@
       </c>
       <c r="D263" s="8" t="inlineStr">
         <is>
-          <t>オプション欄・連絡事項を入力して閉じ、開き直す</t>
+          <t>日程表の色分けを見る</t>
         </is>
       </c>
       <c r="E263" s="8" t="inlineStr">
         <is>
-          <t>入力が保持されている</t>
+          <t>色分けは無く、通)/振)/講)のラベルで区別（注意の赤字は残る）</t>
         </is>
       </c>
       <c r="F263" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="G263" s="10" t="inlineStr">
-        <is>
-          <t>更新</t>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G263" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H263" s="6" t="n"/>
@@ -10500,22 +10500,22 @@
       </c>
       <c r="D264" s="8" t="inlineStr">
         <is>
-          <t>講習の科目が多い生徒をA4横で印刷する</t>
+          <t>日程表のQR表示を見る</t>
         </is>
       </c>
       <c r="E264" s="8" t="inlineStr">
         <is>
-          <t>回数表の下が切れずに1枚に収まる</t>
+          <t>どの教室でも表示される</t>
         </is>
       </c>
       <c r="F264" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="G264" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G264" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H264" s="6" t="n"/>
@@ -10525,9 +10525,9 @@
       <c r="A265" s="6" t="n">
         <v>262</v>
       </c>
-      <c r="B265" s="7" t="inlineStr">
-        <is>
-          <t>24.講師日程表</t>
+      <c r="B265" s="8" t="inlineStr">
+        <is>
+          <t>23.生徒日程表</t>
         </is>
       </c>
       <c r="C265" s="6" t="inlineStr">
@@ -10537,22 +10537,22 @@
       </c>
       <c r="D265" s="8" t="inlineStr">
         <is>
-          <t>講師の日程表を開く</t>
+          <t>日程表の下段の欄を見る</t>
         </is>
       </c>
       <c r="E265" s="8" t="inlineStr">
         <is>
-          <t>別タブでHTML表示される</t>
+          <t>休み欄が無く、振替授業欄が左に寄り、右にオプション欄（2列×5行）がある</t>
         </is>
       </c>
       <c r="F265" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="G265" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G265" s="10" t="inlineStr">
+        <is>
+          <t>更新</t>
         </is>
       </c>
       <c r="H265" s="6" t="n"/>
@@ -10564,7 +10564,7 @@
       </c>
       <c r="B266" s="8" t="inlineStr">
         <is>
-          <t>24.講師日程表</t>
+          <t>23.生徒日程表</t>
         </is>
       </c>
       <c r="C266" s="6" t="inlineStr">
@@ -10574,22 +10574,22 @@
       </c>
       <c r="D266" s="8" t="inlineStr">
         <is>
-          <t>コマの中身を見る</t>
+          <t>オプション欄・連絡事項を入力して閉じ、開き直す</t>
         </is>
       </c>
       <c r="E266" s="8" t="inlineStr">
         <is>
-          <t>縦書きのカードで、名前の下に科目・種別・状態が詰めて表示される（出席は「出」）</t>
+          <t>入力が保持されている</t>
         </is>
       </c>
       <c r="F266" s="6" t="inlineStr">
         <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="G266" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G266" s="10" t="inlineStr">
+        <is>
+          <t>更新</t>
         </is>
       </c>
       <c r="H266" s="6" t="n"/>
@@ -10601,7 +10601,7 @@
       </c>
       <c r="B267" s="8" t="inlineStr">
         <is>
-          <t>24.講師日程表</t>
+          <t>23.生徒日程表</t>
         </is>
       </c>
       <c r="C267" s="6" t="inlineStr">
@@ -10611,17 +10611,17 @@
       </c>
       <c r="D267" s="8" t="inlineStr">
         <is>
-          <t>生徒1人のコマと2人のコマを見比べる</t>
+          <t>講習の科目が多い生徒をA4横で印刷する</t>
         </is>
       </c>
       <c r="E267" s="8" t="inlineStr">
         <is>
-          <t>文字の大きさが同じ（1人だけ大きくならない）</t>
+          <t>回数表の下が切れずに1枚に収まる</t>
         </is>
       </c>
       <c r="F267" s="6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="G267" s="9" t="inlineStr">
@@ -10636,7 +10636,7 @@
       <c r="A268" s="6" t="n">
         <v>265</v>
       </c>
-      <c r="B268" s="8" t="inlineStr">
+      <c r="B268" s="7" t="inlineStr">
         <is>
           <t>24.講師日程表</t>
         </is>
@@ -10648,12 +10648,12 @@
       </c>
       <c r="D268" s="8" t="inlineStr">
         <is>
-          <t>8限×5日のように予定の多い講師を印刷プレビューする</t>
+          <t>講師の日程表を開く</t>
         </is>
       </c>
       <c r="E268" s="8" t="inlineStr">
         <is>
-          <t>A4横1枚に収まる（A3に自動で切り替わらない）</t>
+          <t>別タブでHTML表示される</t>
         </is>
       </c>
       <c r="F268" s="6" t="inlineStr">
@@ -10661,9 +10661,9 @@
           <t>★★</t>
         </is>
       </c>
-      <c r="G268" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+      <c r="G268" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H268" s="6" t="n"/>
@@ -10685,17 +10685,17 @@
       </c>
       <c r="D269" s="8" t="inlineStr">
         <is>
-          <t>給与計算欄を見る</t>
+          <t>コマの中身を見る</t>
         </is>
       </c>
       <c r="E269" s="8" t="inlineStr">
         <is>
-          <t>レッスン行が左右2列に振り分けられ、単価入力と合計が1画面に収まる（縦スクロール枠が無い）</t>
+          <t>縦書きのカードで、名前の下に科目・種別・状態が詰めて表示される（出席は「出」）</t>
         </is>
       </c>
       <c r="F269" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★</t>
         </is>
       </c>
       <c r="G269" s="9" t="inlineStr">
@@ -10722,17 +10722,17 @@
       </c>
       <c r="D270" s="8" t="inlineStr">
         <is>
-          <t>給与計算欄に単価を入れる</t>
+          <t>生徒1人のコマと2人のコマを見比べる</t>
         </is>
       </c>
       <c r="E270" s="8" t="inlineStr">
         <is>
-          <t>小計・合計が正しく計算される</t>
+          <t>文字の大きさが同じ（1人だけ大きくならない）</t>
         </is>
       </c>
       <c r="F270" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★</t>
         </is>
       </c>
       <c r="G270" s="9" t="inlineStr">
@@ -10759,17 +10759,17 @@
       </c>
       <c r="D271" s="8" t="inlineStr">
         <is>
-          <t>下段に振替授業欄があるか見る</t>
+          <t>8限×5日のように予定の多い講師を印刷プレビューする</t>
         </is>
       </c>
       <c r="E271" s="8" t="inlineStr">
         <is>
-          <t>振替授業欄は無い（週グリッド内の振替コマ自体は出る）</t>
+          <t>A4横1枚に収まる（A3に自動で切り替わらない）</t>
         </is>
       </c>
       <c r="F271" s="6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="G271" s="9" t="inlineStr">
@@ -10796,17 +10796,17 @@
       </c>
       <c r="D272" s="8" t="inlineStr">
         <is>
-          <t>休みの生徒が多いコマを見る</t>
+          <t>給与計算欄を見る</t>
         </is>
       </c>
       <c r="E272" s="8" t="inlineStr">
         <is>
-          <t>溢れた休み生徒はセルから間引かれる（ふれるとツールチップには全員出る）</t>
+          <t>レッスン行が左右2列に振り分けられ、単価入力と合計が1画面に収まる（縦スクロール枠が無い）</t>
         </is>
       </c>
       <c r="F272" s="6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="G272" s="9" t="inlineStr">
@@ -10833,22 +10833,22 @@
       </c>
       <c r="D273" s="8" t="inlineStr">
         <is>
-          <t>同コマで生徒を別講師の机へ移動したあと、両方の講師ページを見る</t>
+          <t>給与計算欄に単価を入れる</t>
         </is>
       </c>
       <c r="E273" s="8" t="inlineStr">
         <is>
-          <t>生徒は移動先の講師のページにだけ出る（旧講師のページに残らない）</t>
+          <t>小計・合計が正しく計算される</t>
         </is>
       </c>
       <c r="F273" s="6" t="inlineStr">
         <is>
-          <t>★★★</t>
-        </is>
-      </c>
-      <c r="G273" s="10" t="inlineStr">
-        <is>
-          <t>更新</t>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G273" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H273" s="6" t="n"/>
@@ -10870,22 +10870,22 @@
       </c>
       <c r="D274" s="8" t="inlineStr">
         <is>
-          <t>講師日程表を印刷する</t>
+          <t>下段に振替授業欄があるか見る</t>
         </is>
       </c>
       <c r="E274" s="8" t="inlineStr">
         <is>
-          <t>文字化け・崩れが無い</t>
+          <t>振替授業欄は無い（週グリッド内の振替コマ自体は出る）</t>
         </is>
       </c>
       <c r="F274" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="G274" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G274" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H274" s="6" t="n"/>
@@ -10895,9 +10895,9 @@
       <c r="A275" s="6" t="n">
         <v>272</v>
       </c>
-      <c r="B275" s="7" t="inlineStr">
-        <is>
-          <t>25.日程表コマ組み（別タブD&amp;D）</t>
+      <c r="B275" s="8" t="inlineStr">
+        <is>
+          <t>24.講師日程表</t>
         </is>
       </c>
       <c r="C275" s="6" t="inlineStr">
@@ -10907,17 +10907,17 @@
       </c>
       <c r="D275" s="8" t="inlineStr">
         <is>
-          <t>生徒日程表の授業カード（通/振/講/増コマ）を長押しする</t>
+          <t>休みの生徒が多いコマを見る</t>
         </is>
       </c>
       <c r="E275" s="8" t="inlineStr">
         <is>
-          <t>掴める（集団カード・出欠カードは掴めない）</t>
+          <t>溢れた休み生徒はセルから間引かれる（ふれるとツールチップには全員出る）</t>
         </is>
       </c>
       <c r="F275" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★</t>
         </is>
       </c>
       <c r="G275" s="9" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="B276" s="8" t="inlineStr">
         <is>
-          <t>25.日程表コマ組み（別タブD&amp;D）</t>
+          <t>24.講師日程表</t>
         </is>
       </c>
       <c r="C276" s="6" t="inlineStr">
@@ -10944,22 +10944,22 @@
       </c>
       <c r="D276" s="8" t="inlineStr">
         <is>
-          <t>掴んだカードを空きコマへドラッグする</t>
+          <t>同コマで生徒を別講師の机へ移動したあと、両方の講師ページを見る</t>
         </is>
       </c>
       <c r="E276" s="8" t="inlineStr">
         <is>
-          <t>ドロップ先が青枠でハイライトされる</t>
+          <t>生徒は移動先の講師のページにだけ出る（旧講師のページに残らない）</t>
         </is>
       </c>
       <c r="F276" s="6" t="inlineStr">
         <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="G276" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+          <t>★★★</t>
+        </is>
+      </c>
+      <c r="G276" s="10" t="inlineStr">
+        <is>
+          <t>更新</t>
         </is>
       </c>
       <c r="H276" s="6" t="n"/>
@@ -10971,7 +10971,7 @@
       </c>
       <c r="B277" s="8" t="inlineStr">
         <is>
-          <t>25.日程表コマ組み（別タブD&amp;D）</t>
+          <t>24.講師日程表</t>
         </is>
       </c>
       <c r="C277" s="6" t="inlineStr">
@@ -10981,12 +10981,12 @@
       </c>
       <c r="D277" s="8" t="inlineStr">
         <is>
-          <t>空きコマへドロップする</t>
+          <t>講師日程表を印刷する</t>
         </is>
       </c>
       <c r="E277" s="8" t="inlineStr">
         <is>
-          <t>机選択モーダルが「コマ表の一コマを切り取った表」の形で開く（日付行・時限列つき）</t>
+          <t>文字化け・崩れが無い</t>
         </is>
       </c>
       <c r="F277" s="6" t="inlineStr">
@@ -10994,9 +10994,9 @@
           <t>★★</t>
         </is>
       </c>
-      <c r="G277" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+      <c r="G277" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H277" s="6" t="n"/>
@@ -11006,7 +11006,7 @@
       <c r="A278" s="6" t="n">
         <v>275</v>
       </c>
-      <c r="B278" s="8" t="inlineStr">
+      <c r="B278" s="7" t="inlineStr">
         <is>
           <t>25.日程表コマ組み（別タブD&amp;D）</t>
         </is>
@@ -11018,17 +11018,17 @@
       </c>
       <c r="D278" s="8" t="inlineStr">
         <is>
-          <t>モーダルで空席をクリックする</t>
+          <t>生徒日程表の授業カード（通/振/講/増コマ）を長押しする</t>
         </is>
       </c>
       <c r="E278" s="8" t="inlineStr">
         <is>
-          <t>盤面が実際に移動し、日程表にも反映される</t>
+          <t>掴める（集団カード・出欠カードは掴めない）</t>
         </is>
       </c>
       <c r="F278" s="6" t="inlineStr">
         <is>
-          <t>★★★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="G278" s="9" t="inlineStr">
@@ -11055,17 +11055,17 @@
       </c>
       <c r="D279" s="8" t="inlineStr">
         <is>
-          <t>モーダルで在席の生徒をクリックする</t>
+          <t>掴んだカードを空きコマへドラッグする</t>
         </is>
       </c>
       <c r="E279" s="8" t="inlineStr">
         <is>
-          <t>盤面の入れ替えと同じように2人が交換される</t>
+          <t>ドロップ先が青枠でハイライトされる</t>
         </is>
       </c>
       <c r="F279" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★</t>
         </is>
       </c>
       <c r="G279" s="9" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="D280" s="8" t="inlineStr">
         <is>
-          <t>出席済みの席を選ぼうとする</t>
+          <t>空きコマへドロップする</t>
         </is>
       </c>
       <c r="E280" s="8" t="inlineStr">
         <is>
-          <t>選べない（ブロック表示になる）</t>
+          <t>机選択モーダルが「コマ表の一コマを切り取った表」の形で開く（日付行・時限列つき）</t>
         </is>
       </c>
       <c r="F280" s="6" t="inlineStr">
@@ -11129,17 +11129,17 @@
       </c>
       <c r="D281" s="8" t="inlineStr">
         <is>
-          <t>移動が成立した直後を見る</t>
+          <t>モーダルで空席をクリックする</t>
         </is>
       </c>
       <c r="E281" s="8" t="inlineStr">
         <is>
-          <t>移動先のコマが数秒だけ黄色くハイライトされる</t>
+          <t>盤面が実際に移動し、日程表にも反映される</t>
         </is>
       </c>
       <c r="F281" s="6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★★</t>
         </is>
       </c>
       <c r="G281" s="9" t="inlineStr">
@@ -11166,12 +11166,12 @@
       </c>
       <c r="D282" s="8" t="inlineStr">
         <is>
-          <t>移動できない場所へ落とす</t>
+          <t>モーダルで在席の生徒をクリックする</t>
         </is>
       </c>
       <c r="E282" s="8" t="inlineStr">
         <is>
-          <t>理由が大きく表示され「日程表に戻る」で閉じられる。盤面は変わっていない</t>
+          <t>盤面の入れ替えと同じように2人が交換される</t>
         </is>
       </c>
       <c r="F282" s="6" t="inlineStr">
@@ -11203,17 +11203,17 @@
       </c>
       <c r="D283" s="8" t="inlineStr">
         <is>
-          <t>今の表示から8週間以上離れたコマへ移動しようとする</t>
+          <t>出席済みの席を選ぼうとする</t>
         </is>
       </c>
       <c r="E283" s="8" t="inlineStr">
         <is>
-          <t>成立しない（盤面が重くならない）</t>
+          <t>選べない（ブロック表示になる）</t>
         </is>
       </c>
       <c r="F283" s="6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="G283" s="9" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="D284" s="8" t="inlineStr">
         <is>
-          <t>ブラウザを拡大（120〜150%）した状態で机選択モーダルを開く</t>
+          <t>移動が成立した直後を見る</t>
         </is>
       </c>
       <c r="E284" s="8" t="inlineStr">
         <is>
-          <t>モーダルが画面からはみ出さず全部見える</t>
+          <t>移動先のコマが数秒だけ黄色くハイライトされる</t>
         </is>
       </c>
       <c r="F284" s="6" t="inlineStr">
@@ -11277,17 +11277,17 @@
       </c>
       <c r="D285" s="8" t="inlineStr">
         <is>
-          <t>カードを長押しせず短くタップする</t>
+          <t>移動できない場所へ落とす</t>
         </is>
       </c>
       <c r="E285" s="8" t="inlineStr">
         <is>
-          <t>出席不可のトグルが効く（D&amp;Dに邪魔されない）</t>
+          <t>理由が大きく表示され「日程表に戻る」で閉じられる。盤面は変わっていない</t>
         </is>
       </c>
       <c r="F285" s="6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="G285" s="9" t="inlineStr">
@@ -11314,17 +11314,17 @@
       </c>
       <c r="D286" s="8" t="inlineStr">
         <is>
-          <t>コマ組みで動かしたあとコマ表で「保存」し、再読み込みする</t>
+          <t>今の表示から8週間以上離れたコマへ移動しようとする</t>
         </is>
       </c>
       <c r="E286" s="8" t="inlineStr">
         <is>
-          <t>移動結果が残っている</t>
+          <t>成立しない（盤面が重くならない）</t>
         </is>
       </c>
       <c r="F286" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★</t>
         </is>
       </c>
       <c r="G286" s="9" t="inlineStr">
@@ -11339,9 +11339,9 @@
       <c r="A287" s="6" t="n">
         <v>284</v>
       </c>
-      <c r="B287" s="7" t="inlineStr">
-        <is>
-          <t>26.講習集計・空フォーマット</t>
+      <c r="B287" s="8" t="inlineStr">
+        <is>
+          <t>25.日程表コマ組み（別タブD&amp;D）</t>
         </is>
       </c>
       <c r="C287" s="6" t="inlineStr">
@@ -11351,12 +11351,12 @@
       </c>
       <c r="D287" s="8" t="inlineStr">
         <is>
-          <t>生徒日程表の「講習集計結果」ボタンを探す</t>
+          <t>ブラウザを拡大（120〜150%）した状態で机選択モーダルを開く</t>
         </is>
       </c>
       <c r="E287" s="8" t="inlineStr">
         <is>
-          <t>表示期間に講習期間が重なるときだけ出る</t>
+          <t>モーダルが画面からはみ出さず全部見える</t>
         </is>
       </c>
       <c r="F287" s="6" t="inlineStr">
@@ -11364,9 +11364,9 @@
           <t>★</t>
         </is>
       </c>
-      <c r="G287" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+      <c r="G287" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H287" s="6" t="n"/>
@@ -11378,7 +11378,7 @@
       </c>
       <c r="B288" s="8" t="inlineStr">
         <is>
-          <t>26.講習集計・空フォーマット</t>
+          <t>25.日程表コマ組み（別タブD&amp;D）</t>
         </is>
       </c>
       <c r="C288" s="6" t="inlineStr">
@@ -11388,22 +11388,22 @@
       </c>
       <c r="D288" s="8" t="inlineStr">
         <is>
-          <t>「講習集計結果」を押す</t>
+          <t>カードを長押しせず短くタップする</t>
         </is>
       </c>
       <c r="E288" s="8" t="inlineStr">
         <is>
-          <t>全生徒の登録状況が新しいタブで一覧表示される</t>
+          <t>出席不可のトグルが効く（D&amp;Dに邪魔されない）</t>
         </is>
       </c>
       <c r="F288" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="G288" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G288" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H288" s="6" t="n"/>
@@ -11415,7 +11415,7 @@
       </c>
       <c r="B289" s="8" t="inlineStr">
         <is>
-          <t>26.講習集計・空フォーマット</t>
+          <t>25.日程表コマ組み（別タブD&amp;D）</t>
         </is>
       </c>
       <c r="C289" s="6" t="inlineStr">
@@ -11425,17 +11425,17 @@
       </c>
       <c r="D289" s="8" t="inlineStr">
         <is>
-          <t>一覧の「希望科目（授業時間）」列を見る</t>
+          <t>コマ組みで動かしたあとコマ表で「保存」し、再読み込みする</t>
         </is>
       </c>
       <c r="E289" s="8" t="inlineStr">
         <is>
-          <t>例「英×1 / 数60分×2」のように授業時間つきで出る</t>
+          <t>移動結果が残っている</t>
         </is>
       </c>
       <c r="F289" s="6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="G289" s="9" t="inlineStr">
@@ -11450,7 +11450,7 @@
       <c r="A290" s="6" t="n">
         <v>287</v>
       </c>
-      <c r="B290" s="8" t="inlineStr">
+      <c r="B290" s="7" t="inlineStr">
         <is>
           <t>26.講習集計・空フォーマット</t>
         </is>
@@ -11462,12 +11462,12 @@
       </c>
       <c r="D290" s="8" t="inlineStr">
         <is>
-          <t>一覧の「提出日時」「提出方法」列を見る</t>
+          <t>生徒日程表の「講習集計結果」ボタンを探す</t>
         </is>
       </c>
       <c r="E290" s="8" t="inlineStr">
         <is>
-          <t>QR提出／室長登録の別と日時（M/D HH:MM）が出る（古いデータは —）</t>
+          <t>表示期間に講習期間が重なるときだけ出る</t>
         </is>
       </c>
       <c r="F290" s="6" t="inlineStr">
@@ -11475,9 +11475,9 @@
           <t>★</t>
         </is>
       </c>
-      <c r="G290" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+      <c r="G290" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H290" s="6" t="n"/>
@@ -11499,17 +11499,17 @@
       </c>
       <c r="D291" s="8" t="inlineStr">
         <is>
-          <t>一覧を一番下までスクロールする</t>
+          <t>「講習集計結果」を押す</t>
         </is>
       </c>
       <c r="E291" s="8" t="inlineStr">
         <is>
-          <t>最終行までタスクバーに隠れず見える</t>
+          <t>全生徒の登録状況が新しいタブで一覧表示される</t>
         </is>
       </c>
       <c r="F291" s="6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="G291" s="6" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="D292" s="8" t="inlineStr">
         <is>
-          <t>講師日程表の「講習集計結果」を押す</t>
+          <t>一覧の「希望科目（授業時間）」列を見る</t>
         </is>
       </c>
       <c r="E292" s="8" t="inlineStr">
         <is>
-          <t>講師版（No./講師名/登録状況/提出日時/提出方法の5列）が出る</t>
+          <t>例「英×1 / 数60分×2」のように授業時間つきで出る</t>
         </is>
       </c>
       <c r="F292" s="6" t="inlineStr">
@@ -11573,22 +11573,22 @@
       </c>
       <c r="D293" s="8" t="inlineStr">
         <is>
-          <t>「印刷用全員表示」を押す</t>
+          <t>一覧の「提出日時」「提出方法」列を見る</t>
         </is>
       </c>
       <c r="E293" s="8" t="inlineStr">
         <is>
-          <t>全生徒ぶんが並んで印刷できる</t>
+          <t>QR提出／室長登録の別と日時（M/D HH:MM）が出る（古いデータは —）</t>
         </is>
       </c>
       <c r="F293" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="G293" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G293" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H293" s="6" t="n"/>
@@ -11610,12 +11610,12 @@
       </c>
       <c r="D294" s="8" t="inlineStr">
         <is>
-          <t>空フォーマットを開く</t>
+          <t>一覧を一番下までスクロールする</t>
         </is>
       </c>
       <c r="E294" s="8" t="inlineStr">
         <is>
-          <t>自動では印刷されず、画面に印刷ボタンがある（編集してから印刷できる）</t>
+          <t>最終行までタスクバーに隠れず見える</t>
         </is>
       </c>
       <c r="F294" s="6" t="inlineStr">
@@ -11623,9 +11623,9 @@
           <t>★</t>
         </is>
       </c>
-      <c r="G294" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+      <c r="G294" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H294" s="6" t="n"/>
@@ -11647,17 +11647,17 @@
       </c>
       <c r="D295" s="8" t="inlineStr">
         <is>
-          <t>空フォーマットの連絡事項・オプション欄をクリックする</t>
+          <t>講師日程表の「講習集計結果」を押す</t>
         </is>
       </c>
       <c r="E295" s="8" t="inlineStr">
         <is>
-          <t>入力モードに入って文字を入力できる</t>
+          <t>講師版（No./講師名/登録状況/提出日時/提出方法の5列）が出る</t>
         </is>
       </c>
       <c r="F295" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
+          <t>★</t>
         </is>
       </c>
       <c r="G295" s="9" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="D296" s="8" t="inlineStr">
         <is>
-          <t>空フォーマットに入力して閉じ、開き直す</t>
+          <t>「印刷用全員表示」を押す</t>
         </is>
       </c>
       <c r="E296" s="8" t="inlineStr">
         <is>
-          <t>入力が保持されている。かつ通常の生徒日程表の連絡事項には影響していない</t>
+          <t>全生徒ぶんが並んで印刷できる</t>
         </is>
       </c>
       <c r="F296" s="6" t="inlineStr">
@@ -11697,9 +11697,9 @@
           <t>★★</t>
         </is>
       </c>
-      <c r="G296" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+      <c r="G296" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H296" s="6" t="n"/>
@@ -11721,12 +11721,12 @@
       </c>
       <c r="D297" s="8" t="inlineStr">
         <is>
-          <t>空フォーマットのロゴ・校舎名/TELを見る</t>
+          <t>空フォーマットを開く</t>
         </is>
       </c>
       <c r="E297" s="8" t="inlineStr">
         <is>
-          <t>生徒日程表と同じものが表示される</t>
+          <t>自動では印刷されず、画面に印刷ボタンがある（編集してから印刷できる）</t>
         </is>
       </c>
       <c r="F297" s="6" t="inlineStr">
@@ -11746,9 +11746,9 @@
       <c r="A298" s="6" t="n">
         <v>295</v>
       </c>
-      <c r="B298" s="7" t="inlineStr">
-        <is>
-          <t>27.コマ表PDF・共有</t>
+      <c r="B298" s="8" t="inlineStr">
+        <is>
+          <t>26.講習集計・空フォーマット</t>
         </is>
       </c>
       <c r="C298" s="6" t="inlineStr">
@@ -11758,12 +11758,12 @@
       </c>
       <c r="D298" s="8" t="inlineStr">
         <is>
-          <t>コマ表をPDFに出す</t>
+          <t>空フォーマットの連絡事項・オプション欄をクリックする</t>
         </is>
       </c>
       <c r="E298" s="8" t="inlineStr">
         <is>
-          <t>コマ表本体だけが出る（ストックの操作パネルは入らない）</t>
+          <t>入力モードに入って文字を入力できる</t>
         </is>
       </c>
       <c r="F298" s="6" t="inlineStr">
@@ -11771,9 +11771,9 @@
           <t>★★</t>
         </is>
       </c>
-      <c r="G298" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+      <c r="G298" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H298" s="6" t="n"/>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="B299" s="8" t="inlineStr">
         <is>
-          <t>27.コマ表PDF・共有</t>
+          <t>26.講習集計・空フォーマット</t>
         </is>
       </c>
       <c r="C299" s="6" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="D299" s="8" t="inlineStr">
         <is>
-          <t>出たPDFのレイアウトを見る</t>
+          <t>空フォーマットに入力して閉じ、開き直す</t>
         </is>
       </c>
       <c r="E299" s="8" t="inlineStr">
         <is>
-          <t>A3縦1ページに1週間分が収まる</t>
+          <t>入力が保持されている。かつ通常の生徒日程表の連絡事項には影響していない</t>
         </is>
       </c>
       <c r="F299" s="6" t="inlineStr">
@@ -11808,9 +11808,9 @@
           <t>★★</t>
         </is>
       </c>
-      <c r="G299" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+      <c r="G299" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H299" s="6" t="n"/>
@@ -11822,7 +11822,7 @@
       </c>
       <c r="B300" s="8" t="inlineStr">
         <is>
-          <t>27.コマ表PDF・共有</t>
+          <t>26.講習集計・空フォーマット</t>
         </is>
       </c>
       <c r="C300" s="6" t="inlineStr">
@@ -11832,12 +11832,12 @@
       </c>
       <c r="D300" s="8" t="inlineStr">
         <is>
-          <t>PDFの時間列・生徒名を見る</t>
+          <t>空フォーマットのロゴ・校舎名/TELを見る</t>
         </is>
       </c>
       <c r="E300" s="8" t="inlineStr">
         <is>
-          <t>時間列は中央寄せの大きい文字、生徒名は欠けずに収まる</t>
+          <t>生徒日程表と同じものが表示される</t>
         </is>
       </c>
       <c r="F300" s="6" t="inlineStr">
@@ -11845,9 +11845,9 @@
           <t>★</t>
         </is>
       </c>
-      <c r="G300" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+      <c r="G300" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H300" s="6" t="n"/>
@@ -11857,7 +11857,7 @@
       <c r="A301" s="6" t="n">
         <v>298</v>
       </c>
-      <c r="B301" s="8" t="inlineStr">
+      <c r="B301" s="7" t="inlineStr">
         <is>
           <t>27.コマ表PDF・共有</t>
         </is>
@@ -11869,12 +11869,12 @@
       </c>
       <c r="D301" s="8" t="inlineStr">
         <is>
-          <t>PDFの文字を確認する</t>
+          <t>コマ表をPDFに出す</t>
         </is>
       </c>
       <c r="E301" s="8" t="inlineStr">
         <is>
-          <t>文字化け・崩れが無い</t>
+          <t>コマ表本体だけが出る（ストックの操作パネルは入らない）</t>
         </is>
       </c>
       <c r="F301" s="6" t="inlineStr">
@@ -11906,22 +11906,22 @@
       </c>
       <c r="D302" s="8" t="inlineStr">
         <is>
-          <t>ツールバーの「講師日程共有」を押す</t>
+          <t>出たPDFのレイアウトを見る</t>
         </is>
       </c>
       <c r="E302" s="8" t="inlineStr">
         <is>
-          <t>共有用URLがコピーされる</t>
+          <t>A3縦1ページに1週間分が収まる</t>
         </is>
       </c>
       <c r="F302" s="6" t="inlineStr">
         <is>
-          <t>★</t>
-        </is>
-      </c>
-      <c r="G302" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+          <t>★★</t>
+        </is>
+      </c>
+      <c r="G302" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H302" s="6" t="n"/>
@@ -11943,22 +11943,22 @@
       </c>
       <c r="D303" s="8" t="inlineStr">
         <is>
-          <t>共有URLを別の端末（ログインしていない状態）で開く</t>
+          <t>PDFの時間列・生徒名を見る</t>
         </is>
       </c>
       <c r="E303" s="8" t="inlineStr">
         <is>
-          <t>その日のコマが見え、◀前日/今日/翌日▶・▲前コマ/▼後コマで移動できる</t>
+          <t>時間列は中央寄せの大きい文字、生徒名は欠けずに収まる</t>
         </is>
       </c>
       <c r="F303" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="G303" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G303" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H303" s="6" t="n"/>
@@ -11980,12 +11980,12 @@
       </c>
       <c r="D304" s="8" t="inlineStr">
         <is>
-          <t>共有画面で編集しようとする</t>
+          <t>PDFの文字を確認する</t>
         </is>
       </c>
       <c r="E304" s="8" t="inlineStr">
         <is>
-          <t>閲覧のみで編集できない</t>
+          <t>文字化け・崩れが無い</t>
         </is>
       </c>
       <c r="F304" s="6" t="inlineStr">
@@ -11993,9 +11993,9 @@
           <t>★★</t>
         </is>
       </c>
-      <c r="G304" s="9" t="inlineStr">
-        <is>
-          <t>新規</t>
+      <c r="G304" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
         </is>
       </c>
       <c r="H304" s="6" t="n"/>
@@ -12005,34 +12005,34 @@
       <c r="A305" s="6" t="n">
         <v>302</v>
       </c>
-      <c r="B305" s="7" t="inlineStr">
-        <is>
-          <t>28.全般</t>
+      <c r="B305" s="8" t="inlineStr">
+        <is>
+          <t>27.コマ表PDF・共有</t>
         </is>
       </c>
       <c r="C305" s="6" t="inlineStr">
         <is>
-          <t>共通</t>
+          <t>室長</t>
         </is>
       </c>
       <c r="D305" s="8" t="inlineStr">
         <is>
-          <t>ひととおり操作して画面の動きを見る</t>
+          <t>ツールバーの「講師日程共有」を押す</t>
         </is>
       </c>
       <c r="E305" s="8" t="inlineStr">
         <is>
-          <t>固まったり真っ白になったりしない</t>
+          <t>共有用URLがコピーされる</t>
         </is>
       </c>
       <c r="F305" s="6" t="inlineStr">
         <is>
-          <t>★★</t>
-        </is>
-      </c>
-      <c r="G305" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G305" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H305" s="6" t="n"/>
@@ -12044,22 +12044,22 @@
       </c>
       <c r="B306" s="8" t="inlineStr">
         <is>
-          <t>28.全般</t>
+          <t>27.コマ表PDF・共有</t>
         </is>
       </c>
       <c r="C306" s="6" t="inlineStr">
         <is>
-          <t>共通</t>
+          <t>室長</t>
         </is>
       </c>
       <c r="D306" s="8" t="inlineStr">
         <is>
-          <t>操作中にエラー表示が出ないか見る</t>
+          <t>共有URLを別の端末（ログインしていない状態）で開く</t>
         </is>
       </c>
       <c r="E306" s="8" t="inlineStr">
         <is>
-          <t>英語のエラーなどが出ない</t>
+          <t>その日のコマが見え、◀前日/今日/翌日▶・▲前コマ/▼後コマで移動できる</t>
         </is>
       </c>
       <c r="F306" s="6" t="inlineStr">
@@ -12067,9 +12067,9 @@
           <t>★★</t>
         </is>
       </c>
-      <c r="G306" s="6" t="inlineStr">
-        <is>
-          <t>継続</t>
+      <c r="G306" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
         </is>
       </c>
       <c r="H306" s="6" t="n"/>
@@ -12081,27 +12081,27 @@
       </c>
       <c r="B307" s="8" t="inlineStr">
         <is>
-          <t>28.全般</t>
+          <t>27.コマ表PDF・共有</t>
         </is>
       </c>
       <c r="C307" s="6" t="inlineStr">
         <is>
-          <t>共通</t>
+          <t>室長</t>
         </is>
       </c>
       <c r="D307" s="8" t="inlineStr">
         <is>
-          <t>30分ほど連続で操作を続ける</t>
+          <t>共有画面で編集しようとする</t>
         </is>
       </c>
       <c r="E307" s="8" t="inlineStr">
         <is>
-          <t>だんだん重くなったりタブが落ちたりしない</t>
+          <t>閲覧のみで編集できない</t>
         </is>
       </c>
       <c r="F307" s="6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="G307" s="9" t="inlineStr">
@@ -12116,7 +12116,7 @@
       <c r="A308" s="6" t="n">
         <v>305</v>
       </c>
-      <c r="B308" s="8" t="inlineStr">
+      <c r="B308" s="7" t="inlineStr">
         <is>
           <t>28.全般</t>
         </is>
@@ -12128,17 +12128,17 @@
       </c>
       <c r="D308" s="8" t="inlineStr">
         <is>
-          <t>スマホ／タブレットで主要な操作をする</t>
+          <t>ひととおり操作して画面の動きを見る</t>
         </is>
       </c>
       <c r="E308" s="8" t="inlineStr">
         <is>
-          <t>問題なく操作できる</t>
+          <t>固まったり真っ白になったりしない</t>
         </is>
       </c>
       <c r="F308" s="6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="G308" s="6" t="inlineStr">
@@ -12165,17 +12165,17 @@
       </c>
       <c r="D309" s="8" t="inlineStr">
         <is>
-          <t>全体の文字・表示の崩れを見る</t>
+          <t>操作中にエラー表示が出ないか見る</t>
         </is>
       </c>
       <c r="E309" s="8" t="inlineStr">
         <is>
-          <t>文字切れ・はみ出しが無い</t>
+          <t>英語のエラーなどが出ない</t>
         </is>
       </c>
       <c r="F309" s="6" t="inlineStr">
         <is>
-          <t>★</t>
+          <t>★★</t>
         </is>
       </c>
       <c r="G309" s="6" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="D310" s="8" t="inlineStr">
         <is>
-          <t>新しい版がデプロイされた直後にアプリを開く</t>
+          <t>30分ほど連続で操作を続ける</t>
         </is>
       </c>
       <c r="E310" s="8" t="inlineStr">
         <is>
-          <t>自動的に最新版へ読み込み直される（古い画面のまま使わされない）</t>
+          <t>だんだん重くなったりタブが落ちたりしない</t>
         </is>
       </c>
       <c r="F310" s="6" t="inlineStr">
@@ -12223,13 +12223,124 @@
       <c r="H310" s="6" t="n"/>
       <c r="I310" s="8" t="n"/>
     </row>
+    <row r="311">
+      <c r="A311" s="6" t="n">
+        <v>308</v>
+      </c>
+      <c r="B311" s="8" t="inlineStr">
+        <is>
+          <t>28.全般</t>
+        </is>
+      </c>
+      <c r="C311" s="6" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="D311" s="8" t="inlineStr">
+        <is>
+          <t>スマホ／タブレットで主要な操作をする</t>
+        </is>
+      </c>
+      <c r="E311" s="8" t="inlineStr">
+        <is>
+          <t>問題なく操作できる</t>
+        </is>
+      </c>
+      <c r="F311" s="6" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G311" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
+        </is>
+      </c>
+      <c r="H311" s="6" t="n"/>
+      <c r="I311" s="8" t="n"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="6" t="n">
+        <v>309</v>
+      </c>
+      <c r="B312" s="8" t="inlineStr">
+        <is>
+          <t>28.全般</t>
+        </is>
+      </c>
+      <c r="C312" s="6" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="D312" s="8" t="inlineStr">
+        <is>
+          <t>全体の文字・表示の崩れを見る</t>
+        </is>
+      </c>
+      <c r="E312" s="8" t="inlineStr">
+        <is>
+          <t>文字切れ・はみ出しが無い</t>
+        </is>
+      </c>
+      <c r="F312" s="6" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G312" s="6" t="inlineStr">
+        <is>
+          <t>継続</t>
+        </is>
+      </c>
+      <c r="H312" s="6" t="n"/>
+      <c r="I312" s="8" t="n"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="6" t="n">
+        <v>310</v>
+      </c>
+      <c r="B313" s="8" t="inlineStr">
+        <is>
+          <t>28.全般</t>
+        </is>
+      </c>
+      <c r="C313" s="6" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="D313" s="8" t="inlineStr">
+        <is>
+          <t>新しい版がデプロイされた直後にアプリを開く</t>
+        </is>
+      </c>
+      <c r="E313" s="8" t="inlineStr">
+        <is>
+          <t>自動的に最新版へ読み込み直される（古い画面のまま使わされない）</t>
+        </is>
+      </c>
+      <c r="F313" s="6" t="inlineStr">
+        <is>
+          <t>★</t>
+        </is>
+      </c>
+      <c r="G313" s="9" t="inlineStr">
+        <is>
+          <t>新規</t>
+        </is>
+      </c>
+      <c r="H313" s="6" t="n"/>
+      <c r="I313" s="8" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:I310"/>
+  <autoFilter ref="A3:I313"/>
   <mergeCells count="1">
     <mergeCell ref="A2:I2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="H4:H310" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="○ / × / 未 から選んでください" type="list">
+    <dataValidation sqref="H4:H313" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="○ / × / 未 から選んでください" type="list">
       <formula1>"○,×,未"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12409,16 +12520,16 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D9" s="13" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -12846,16 +12957,16 @@
         </is>
       </c>
       <c r="B32" s="15" t="n">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C32" s="15" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D32" s="15" t="n">
         <v>21</v>
       </c>
       <c r="E32" s="15" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/docs/runbooks/コマ表アプリ動作チェックリスト（全項目・網羅版）.xlsx
+++ b/docs/runbooks/コマ表アプリ動作チェックリスト（全項目・網羅版）.xlsx
@@ -523,7 +523,6 @@
       <c r="B1" s="2" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -563,7 +562,6 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
@@ -647,7 +645,6 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
@@ -695,7 +692,6 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
@@ -743,7 +739,6 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
@@ -3586,7 +3581,7 @@
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>赤文字は「出席不可コマに配置」または「講師が選ばれていない机に配置」のときだけ</t>
+          <t>赤文字は「出席不可コマに配置」または「講師が選ばれていない机に配置」のときだけ（承認して黄色にしたコマは出席可能コマ扱いなので赤くならない）</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
@@ -8507,7 +8502,7 @@
       </c>
       <c r="E210" s="8" t="inlineStr">
         <is>
-          <t>戻す操作は無い（一方通行）</t>
+          <t>戻す操作は無い（一方通行）。配置を削除しても、登録を解除しても黄色のまま（戻すのはQRからの新規提出のみ）</t>
         </is>
       </c>
       <c r="F210" s="6" t="inlineStr">
@@ -8517,7 +8512,7 @@
       </c>
       <c r="G210" s="9" t="inlineStr">
         <is>
-          <t>新規</t>
+          <t>更新</t>
         </is>
       </c>
       <c r="H210" s="6" t="n"/>

--- a/docs/runbooks/コマ表アプリ動作チェックリスト（全項目・網羅版）.xlsx
+++ b/docs/runbooks/コマ表アプリ動作チェックリスト（全項目・網羅版）.xlsx
@@ -801,7 +801,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>コマ表アプリ　動作チェックリスト（全項目・網羅版）　v1.5.455 時点</t>
+          <t>コマ表アプリ　動作チェックリスト（全項目・網羅版）　v1.5.484 時点</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>2つ目は「このタブは利用できません」となり、1教室1タブに制限される</t>
+          <t>同じブラウザの2つ目のタブは「このタブは利用できません」になる（※別ブラウザ・別端末は制限対象外＝仕様。多端末の上書きは保存時の版数照合で防ぐ）</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>新規</t>
+          <t>更新</t>
         </is>
       </c>
       <c r="H24" s="6" t="n"/>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>「自動保存しました。」と表示される</t>
+          <t>保存ボタンが「最新データ」に変わる（同期表示が出ていないときは「自動保存しました。」のトーストも出る）</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
@@ -2286,7 +2286,7 @@
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>常に表示され、緑色（グレーアウトしない）</t>
+          <t>常に表示され、青色（グレーアウトしない）。状態は色ではなくラベルで分かる：保存／最新データ／保存中…</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>継続</t>
+          <t>更新</t>
         </is>
       </c>
       <c r="H42" s="6" t="n"/>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>緑のままで何も起きない（押しても問題ない）</t>
+          <t>「最新データ」表示のままで何も起きない（押しても問題ない）</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>継続</t>
+          <t>更新</t>
         </is>
       </c>
       <c r="H44" s="6" t="n"/>
@@ -3618,7 +3618,7 @@
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>名前は赤くならず、ツールチップで理由が読める</t>
+          <t>名前は赤くならず、ツールチップで理由が読める（※承認して黄色にしたコマは警告自体が無いのでツールチップにも出ない）</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="E146" s="8" t="inlineStr">
         <is>
-          <t>削除でき、希望数は変わらない（戻しはできない）</t>
+          <t>削除でき、希望数も1減る（手動追加分も1コマ分の希望として数えるため。戻しはできない）</t>
         </is>
       </c>
       <c r="F146" s="6" t="inlineStr">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="G146" s="6" t="inlineStr">
         <is>
-          <t>継続</t>
+          <t>更新</t>
         </is>
       </c>
       <c r="H146" s="6" t="n"/>
@@ -6319,7 +6319,7 @@
       </c>
       <c r="E151" s="8" t="inlineStr">
         <is>
-          <t>その講師だけ外れ、生徒の講習予定は残る</t>
+          <t>その講師だけ外れ、生徒の講習予定は残る（※外れるのはQR／日程表の登録で置かれた机だけ。室長が手で置いた机は残るのが正）</t>
         </is>
       </c>
       <c r="F151" s="6" t="inlineStr">
@@ -6329,7 +6329,7 @@
       </c>
       <c r="G151" s="6" t="inlineStr">
         <is>
-          <t>継続</t>
+          <t>更新</t>
         </is>
       </c>
       <c r="H151" s="6" t="n"/>
@@ -8317,7 +8317,7 @@
       </c>
       <c r="E205" s="8" t="inlineStr">
         <is>
-          <t>赤い警告が消え、自動割振・自動配置の候補にもなる</t>
+          <t>赤い警告が消え、自動割振・自動配置の候補になる（埋まらないときは「その机に講師が居るか」「同じ時限に本人が居ないか」「制約事項ルールで除外されていないか」を確認）</t>
         </is>
       </c>
       <c r="F205" s="6" t="inlineStr">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="G205" s="9" t="inlineStr">
         <is>
-          <t>新規</t>
+          <t>更新</t>
         </is>
       </c>
       <c r="H205" s="6" t="n"/>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="E237" s="8" t="inlineStr">
         <is>
-          <t>対象・除外を指定でき、重なったら除外が優先される</t>
+          <t>対象・除外を指定でき、重なったら除外が優先される（※同じグループの別ルールに割り当て済みの学年は選択肢から消えるのが正）</t>
         </is>
       </c>
       <c r="F237" s="6" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="G237" s="6" t="inlineStr">
         <is>
-          <t>継続</t>
+          <t>更新</t>
         </is>
       </c>
       <c r="H237" s="6" t="n"/>
@@ -9982,7 +9982,7 @@
       </c>
       <c r="E250" s="8" t="inlineStr">
         <is>
-          <t>校舎名・ロゴは共通、期間は生徒/講師で別に保てる</t>
+          <t>校舎名・ロゴは共通、期間は生徒/講師で別に保てる（※室長画面で校舎名・ロゴを設定してから確認する）</t>
         </is>
       </c>
       <c r="F250" s="6" t="inlineStr">
@@ -9992,7 +9992,7 @@
       </c>
       <c r="G250" s="6" t="inlineStr">
         <is>
-          <t>継続</t>
+          <t>更新</t>
         </is>
       </c>
       <c r="H250" s="6" t="n"/>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="E262" s="8" t="inlineStr">
         <is>
-          <t>「社」の直後に1行だけ出る（理と社で2行に増えない）</t>
+          <t>「社」の直後に1行だけ出る（理と社で2行に増えない）。※小学生限定。中学生は集団理科＝集理／集団社会＝集社として別に出るのが正</t>
         </is>
       </c>
       <c r="F262" s="6" t="inlineStr">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="G262" s="9" t="inlineStr">
         <is>
-          <t>新規</t>
+          <t>更新</t>
         </is>
       </c>
       <c r="H262" s="6" t="n"/>
